--- a/database/event/8240/event_8240_evp_summary.xlsx
+++ b/database/event/8240/event_8240_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8240" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8240" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>7.1606</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7733</v>
+        <v>4.2275</v>
       </c>
       <c r="E2" t="n">
         <v>11.5076</v>
@@ -548,7 +548,7 @@
         <v>4.2865</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0643</v>
+        <v>2.3615</v>
       </c>
       <c r="E3" t="n">
         <v>6.8886</v>
@@ -594,7 +594,7 @@
         <v>4.2571</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0468</v>
+        <v>2.3424</v>
       </c>
       <c r="E4" t="n">
         <v>6.8414</v>
@@ -640,7 +640,7 @@
         <v>3.9407</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8587</v>
+        <v>2.137</v>
       </c>
       <c r="E5" t="n">
         <v>6.333</v>
@@ -686,7 +686,7 @@
         <v>3.3187</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4888</v>
+        <v>1.7332</v>
       </c>
       <c r="E6" t="n">
         <v>5.3333</v>
@@ -732,7 +732,7 @@
         <v>3.2714</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4607</v>
+        <v>1.7025</v>
       </c>
       <c r="E7" t="n">
         <v>5.2574</v>
@@ -778,7 +778,7 @@
         <v>3.2712</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4606</v>
+        <v>1.7023</v>
       </c>
       <c r="E8" t="n">
         <v>5.257</v>
@@ -824,7 +824,7 @@
         <v>3.0399</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3231</v>
+        <v>1.5522</v>
       </c>
       <c r="E9" t="n">
         <v>4.8853</v>
@@ -870,7 +870,7 @@
         <v>2.8811</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2286</v>
+        <v>1.4491</v>
       </c>
       <c r="E10" t="n">
         <v>4.6301</v>
@@ -916,7 +916,7 @@
         <v>2.6578</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0959</v>
+        <v>1.3041</v>
       </c>
       <c r="E11" t="n">
         <v>4.2713</v>
@@ -962,7 +962,7 @@
         <v>2.2432</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8493000000000001</v>
+        <v>1.0349</v>
       </c>
       <c r="E12" t="n">
         <v>3.6049</v>
@@ -1008,7 +1008,7 @@
         <v>2.2061</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8273</v>
+        <v>1.0109</v>
       </c>
       <c r="E13" t="n">
         <v>3.5454</v>
@@ -1054,7 +1054,7 @@
         <v>2.0987</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7634</v>
+        <v>0.9412</v>
       </c>
       <c r="E14" t="n">
         <v>3.3728</v>
@@ -1100,7 +1100,7 @@
         <v>2.076</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7499</v>
+        <v>0.9264</v>
       </c>
       <c r="E15" t="n">
         <v>3.3362</v>
@@ -1146,7 +1146,7 @@
         <v>2.0384</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7276</v>
+        <v>0.902</v>
       </c>
       <c r="E16" t="n">
         <v>3.2759</v>
@@ -1192,7 +1192,7 @@
         <v>1.7398</v>
       </c>
       <c r="D17" t="n">
-        <v>0.55</v>
+        <v>0.7081</v>
       </c>
       <c r="E17" t="n">
         <v>2.7959</v>
@@ -1238,7 +1238,7 @@
         <v>1.6916</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5213</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>2.7185</v>
@@ -1284,7 +1284,7 @@
         <v>1.6141</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4753</v>
+        <v>0.6266</v>
       </c>
       <c r="E19" t="n">
         <v>2.594</v>
@@ -1330,7 +1330,7 @@
         <v>1.4927</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4031</v>
+        <v>0.5477</v>
       </c>
       <c r="E20" t="n">
         <v>2.3989</v>
@@ -1376,7 +1376,7 @@
         <v>1.4686</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3888</v>
+        <v>0.5321</v>
       </c>
       <c r="E21" t="n">
         <v>2.3602</v>
@@ -1422,7 +1422,7 @@
         <v>1.4083</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3529</v>
+        <v>0.493</v>
       </c>
       <c r="E22" t="n">
         <v>2.2633</v>
@@ -1468,7 +1468,7 @@
         <v>1.3468</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3163</v>
+        <v>0.453</v>
       </c>
       <c r="E23" t="n">
         <v>2.1644</v>
@@ -1514,7 +1514,7 @@
         <v>1.3425</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3138</v>
+        <v>0.4502</v>
       </c>
       <c r="E24" t="n">
         <v>2.1575</v>
@@ -1560,7 +1560,7 @@
         <v>1.3313</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3071</v>
+        <v>0.4429</v>
       </c>
       <c r="E25" t="n">
         <v>2.1395</v>
@@ -1606,7 +1606,7 @@
         <v>1.3174</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2988</v>
+        <v>0.4339</v>
       </c>
       <c r="E26" t="n">
         <v>2.1171</v>
@@ -1652,7 +1652,7 @@
         <v>1.0943</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1662</v>
+        <v>0.2891</v>
       </c>
       <c r="E27" t="n">
         <v>1.7586</v>
@@ -1698,7 +1698,7 @@
         <v>1.09</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1636</v>
+        <v>0.2863</v>
       </c>
       <c r="E28" t="n">
         <v>1.7517</v>
@@ -1744,7 +1744,7 @@
         <v>0.9764</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0961</v>
+        <v>0.2125</v>
       </c>
       <c r="E29" t="n">
         <v>1.5691</v>
@@ -1790,7 +1790,7 @@
         <v>0.8326</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0105</v>
+        <v>0.1192</v>
       </c>
       <c r="E30" t="n">
         <v>1.338</v>
@@ -1836,7 +1836,7 @@
         <v>0.8284</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0081</v>
+        <v>0.1165</v>
       </c>
       <c r="E31" t="n">
         <v>1.3313</v>
@@ -1882,7 +1882,7 @@
         <v>0.8168</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0011</v>
+        <v>0.1089</v>
       </c>
       <c r="E32" t="n">
         <v>1.3126</v>
@@ -1928,7 +1928,7 @@
         <v>0.7992</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.0975</v>
       </c>
       <c r="E33" t="n">
         <v>1.2843</v>
@@ -1974,7 +1974,7 @@
         <v>0.7491</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0391</v>
+        <v>0.065</v>
       </c>
       <c r="E34" t="n">
         <v>1.2039</v>
@@ -2020,7 +2020,7 @@
         <v>0.7325</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.049</v>
+        <v>0.0542</v>
       </c>
       <c r="E35" t="n">
         <v>1.1771</v>
@@ -2066,7 +2066,7 @@
         <v>0.729</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.051</v>
+        <v>0.0519</v>
       </c>
       <c r="E36" t="n">
         <v>1.1716</v>
@@ -2112,7 +2112,7 @@
         <v>0.6969</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0702</v>
+        <v>0.0311</v>
       </c>
       <c r="E37" t="n">
         <v>1.1199</v>
@@ -2158,7 +2158,7 @@
         <v>0.6729000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0844</v>
+        <v>0.0155</v>
       </c>
       <c r="E38" t="n">
         <v>1.0814</v>
@@ -2204,7 +2204,7 @@
         <v>0.6008</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1272</v>
+        <v>-0.0313</v>
       </c>
       <c r="E39" t="n">
         <v>0.9656</v>
@@ -2250,7 +2250,7 @@
         <v>0.5919</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1326</v>
+        <v>-0.0371</v>
       </c>
       <c r="E40" t="n">
         <v>0.9512</v>
@@ -2296,7 +2296,7 @@
         <v>0.5786</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1405</v>
+        <v>-0.0457</v>
       </c>
       <c r="E41" t="n">
         <v>0.9298</v>
@@ -2342,7 +2342,7 @@
         <v>0.5682</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1466</v>
+        <v>-0.0524</v>
       </c>
       <c r="E42" t="n">
         <v>0.9132</v>
@@ -2388,7 +2388,7 @@
         <v>0.4811</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1985</v>
+        <v>-0.109</v>
       </c>
       <c r="E43" t="n">
         <v>0.7731</v>
@@ -2434,7 +2434,7 @@
         <v>0.4798</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1992</v>
+        <v>-0.1099</v>
       </c>
       <c r="E44" t="n">
         <v>0.771</v>
@@ -2480,7 +2480,7 @@
         <v>0.4056</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2434</v>
+        <v>-0.158</v>
       </c>
       <c r="E45" t="n">
         <v>0.6518</v>
@@ -2526,7 +2526,7 @@
         <v>0.2856</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3147</v>
+        <v>-0.236</v>
       </c>
       <c r="E46" t="n">
         <v>0.4589</v>
@@ -2572,7 +2572,7 @@
         <v>0.1881</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3727</v>
+        <v>-0.2992</v>
       </c>
       <c r="E47" t="n">
         <v>0.3023</v>
@@ -2618,7 +2618,7 @@
         <v>0.179</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3781</v>
+        <v>-0.3052</v>
       </c>
       <c r="E48" t="n">
         <v>0.2876</v>
@@ -2664,7 +2664,7 @@
         <v>0.1396</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4015</v>
+        <v>-0.3307</v>
       </c>
       <c r="E49" t="n">
         <v>0.2244</v>
@@ -2710,7 +2710,7 @@
         <v>0.0486</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4556</v>
+        <v>-0.3898</v>
       </c>
       <c r="E50" t="n">
         <v>0.0781</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0437</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5105</v>
+        <v>-0.4497</v>
       </c>
       <c r="E51" t="n">
         <v>-0.0702</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1347</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5646</v>
+        <v>-0.5088</v>
       </c>
       <c r="E52" t="n">
         <v>-0.2164</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1478</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5724</v>
+        <v>-0.5173</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2375</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1577</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5783</v>
+        <v>-0.5238</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2535</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1796</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5913</v>
+        <v>-0.538</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2887</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2471</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6314</v>
+        <v>-0.5818</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3971</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2544</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6358</v>
+        <v>-0.5865</v>
       </c>
       <c r="E57" t="n">
         <v>-0.4088</v>
@@ -3078,7 +3078,7 @@
         <v>-0.3306</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6811</v>
+        <v>-0.636</v>
       </c>
       <c r="E58" t="n">
         <v>-0.5313</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3892</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.716</v>
+        <v>-0.6741</v>
       </c>
       <c r="E59" t="n">
         <v>-0.6254999999999999</v>
@@ -3170,7 +3170,7 @@
         <v>-0.4622</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7594</v>
+        <v>-0.7214</v>
       </c>
       <c r="E60" t="n">
         <v>-0.7428</v>
@@ -3216,7 +3216,7 @@
         <v>-0.492</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7771</v>
+        <v>-0.7408</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7907</v>
@@ -3262,7 +3262,7 @@
         <v>-0.4939</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7782</v>
+        <v>-0.742</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7937</v>
@@ -3308,7 +3308,7 @@
         <v>-0.5317</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8006</v>
+        <v>-0.7665</v>
       </c>
       <c r="E63" t="n">
         <v>-0.8544</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5435</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8077</v>
+        <v>-0.7742</v>
       </c>
       <c r="E64" t="n">
         <v>-0.8734</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5775</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8279</v>
+        <v>-0.7963</v>
       </c>
       <c r="E65" t="n">
         <v>-0.9281</v>
@@ -3446,7 +3446,7 @@
         <v>-0.5793</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.829</v>
+        <v>-0.7975</v>
       </c>
       <c r="E66" t="n">
         <v>-0.931</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5953000000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8385</v>
+        <v>-0.8078</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9567</v>
@@ -3538,7 +3538,7 @@
         <v>-0.6073</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8456</v>
+        <v>-0.8156</v>
       </c>
       <c r="E68" t="n">
         <v>-0.976</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6094000000000001</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8469</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9794</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6447000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8679</v>
+        <v>-0.8399</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0361</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6471</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8693</v>
+        <v>-0.8415</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0399</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6953</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.898</v>
+        <v>-0.8728</v>
       </c>
       <c r="E72" t="n">
         <v>-1.1174</v>
@@ -3768,7 +3768,7 @@
         <v>-0.7035</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9028</v>
+        <v>-0.8781</v>
       </c>
       <c r="E73" t="n">
         <v>-1.1306</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7573</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9348</v>
+        <v>-0.913</v>
       </c>
       <c r="E74" t="n">
         <v>-1.2171</v>
@@ -3860,7 +3860,7 @@
         <v>-0.835</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.981</v>
+        <v>-0.9635</v>
       </c>
       <c r="E75" t="n">
         <v>-1.3419</v>
@@ -3906,7 +3906,7 @@
         <v>-1.1148</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1474</v>
+        <v>-1.1451</v>
       </c>
       <c r="E76" t="n">
         <v>-1.7916</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1161</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1482</v>
+        <v>-1.146</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7937</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1434</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1644</v>
+        <v>-1.1637</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8375</v>
@@ -4044,7 +4044,7 @@
         <v>-1.4588</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3519</v>
+        <v>-1.3684</v>
       </c>
       <c r="E79" t="n">
         <v>-2.3444</v>
@@ -4090,7 +4090,7 @@
         <v>-1.4834</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3666</v>
+        <v>-1.3844</v>
       </c>
       <c r="E80" t="n">
         <v>-2.3839</v>
@@ -4136,7 +4136,7 @@
         <v>-1.6162</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4456</v>
+        <v>-1.4707</v>
       </c>
       <c r="E81" t="n">
         <v>-2.5974</v>

--- a/database/event/8240/event_8240_evp_summary.xlsx
+++ b/database/event/8240/event_8240_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>7.1606</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2275</v>
+        <v>4.1407</v>
       </c>
       <c r="E2" t="n">
         <v>11.5076</v>
@@ -548,7 +548,7 @@
         <v>4.2865</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3615</v>
+        <v>2.3005</v>
       </c>
       <c r="E3" t="n">
         <v>6.8886</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8414</v>
+        <v>6.8187</v>
       </c>
       <c r="C4" t="n">
-        <v>4.2571</v>
+        <v>4.243</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3424</v>
+        <v>2.2727</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8414</v>
+        <v>6.8187</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5171</v>
+        <v>4.4944</v>
       </c>
       <c r="G4" t="n">
         <v>2.3242</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7798</v>
+        <v>4.7442</v>
       </c>
       <c r="I4" t="n">
         <v>4.8244</v>
@@ -640,7 +640,7 @@
         <v>3.9407</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137</v>
+        <v>2.0792</v>
       </c>
       <c r="E5" t="n">
         <v>6.333</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3333</v>
+        <v>5.3083</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3187</v>
+        <v>3.3031</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7332</v>
+        <v>1.6709</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3333</v>
+        <v>5.3083</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3496</v>
+        <v>3.3247</v>
       </c>
       <c r="G6" t="n">
         <v>1.9836</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3496</v>
+        <v>3.3247</v>
       </c>
       <c r="I6" t="n">
         <v>3.3809</v>
@@ -732,7 +732,7 @@
         <v>3.2714</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7025</v>
+        <v>1.6506</v>
       </c>
       <c r="E7" t="n">
         <v>5.2574</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.257</v>
+        <v>5.2367</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2712</v>
+        <v>3.2586</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7023</v>
+        <v>1.6424</v>
       </c>
       <c r="E8" t="n">
-        <v>5.257</v>
+        <v>5.2367</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1987</v>
+        <v>4.1784</v>
       </c>
       <c r="G8" t="n">
         <v>1.0583</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2806</v>
+        <v>4.2487</v>
       </c>
       <c r="I8" t="n">
         <v>4.3205</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.8853</v>
+        <v>4.8738</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0399</v>
+        <v>3.0327</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5522</v>
+        <v>1.4978</v>
       </c>
       <c r="E9" t="n">
-        <v>4.8853</v>
+        <v>4.8738</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5437</v>
+        <v>1.5322</v>
       </c>
       <c r="G9" t="n">
         <v>3.3416</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5437</v>
+        <v>1.5322</v>
       </c>
       <c r="I9" t="n">
         <v>1.5581</v>
@@ -870,7 +870,7 @@
         <v>2.8811</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4491</v>
+        <v>1.4007</v>
       </c>
       <c r="E10" t="n">
         <v>4.6301</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.2713</v>
+        <v>4.2609</v>
       </c>
       <c r="C11" t="n">
-        <v>2.6578</v>
+        <v>2.6514</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3041</v>
+        <v>1.2536</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2713</v>
+        <v>4.2609</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2713</v>
+        <v>4.2609</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3944</v>
+        <v>4.378</v>
       </c>
       <c r="I11" t="n">
         <v>4.4149</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6049</v>
+        <v>3.5915</v>
       </c>
       <c r="C12" t="n">
-        <v>2.2432</v>
+        <v>2.2348</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0349</v>
+        <v>0.9869</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6049</v>
+        <v>3.5915</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6049</v>
+        <v>3.5915</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6049</v>
+        <v>3.5915</v>
       </c>
       <c r="I12" t="n">
         <v>3.6217</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5454</v>
+        <v>3.5321</v>
       </c>
       <c r="C13" t="n">
-        <v>2.2061</v>
+        <v>2.1979</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0109</v>
+        <v>0.9633</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5454</v>
+        <v>3.5321</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5454</v>
+        <v>3.5321</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5454</v>
+        <v>3.5321</v>
       </c>
       <c r="I13" t="n">
         <v>3.5619</v>
@@ -1054,7 +1054,7 @@
         <v>2.0987</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9412</v>
+        <v>0.8998</v>
       </c>
       <c r="E14" t="n">
         <v>3.3728</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.3362</v>
+        <v>3.3159</v>
       </c>
       <c r="C15" t="n">
-        <v>2.076</v>
+        <v>2.0633</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9264</v>
+        <v>0.8771</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3362</v>
+        <v>3.3159</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7339</v>
+        <v>2.7136</v>
       </c>
       <c r="G15" t="n">
         <v>0.6022999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7339</v>
+        <v>2.7136</v>
       </c>
       <c r="I15" t="n">
         <v>2.7595</v>
@@ -1146,7 +1146,7 @@
         <v>2.0384</v>
       </c>
       <c r="D16" t="n">
-        <v>0.902</v>
+        <v>0.8612</v>
       </c>
       <c r="E16" t="n">
         <v>3.2759</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7959</v>
+        <v>2.7869</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7398</v>
+        <v>1.7342</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7081</v>
+        <v>0.6664</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7959</v>
+        <v>2.7869</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4258</v>
+        <v>2.4168</v>
       </c>
       <c r="G17" t="n">
         <v>0.3701</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4258</v>
+        <v>2.4168</v>
       </c>
       <c r="I17" t="n">
         <v>2.4371</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.7185</v>
+        <v>2.7046</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6916</v>
+        <v>1.6829</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7185</v>
+        <v>2.7046</v>
       </c>
       <c r="F18" t="n">
-        <v>3.7143</v>
+        <v>3.7004</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9958</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7143</v>
+        <v>3.7004</v>
       </c>
       <c r="I18" t="n">
         <v>3.7316</v>
@@ -1284,7 +1284,7 @@
         <v>1.6141</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6266</v>
+        <v>0.5895</v>
       </c>
       <c r="E19" t="n">
         <v>2.594</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3989</v>
+        <v>2.39</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4927</v>
+        <v>1.4872</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5477</v>
+        <v>0.5083</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3989</v>
+        <v>2.39</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3691</v>
+        <v>2.3602</v>
       </c>
       <c r="G20" t="n">
         <v>0.0298</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3691</v>
+        <v>2.3602</v>
       </c>
       <c r="I20" t="n">
         <v>2.3801</v>
@@ -1376,7 +1376,7 @@
         <v>1.4686</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5321</v>
+        <v>0.4964</v>
       </c>
       <c r="E21" t="n">
         <v>2.3602</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.2633</v>
+        <v>2.2548</v>
       </c>
       <c r="C22" t="n">
-        <v>1.4083</v>
+        <v>1.4031</v>
       </c>
       <c r="D22" t="n">
-        <v>0.493</v>
+        <v>0.4544</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2633</v>
+        <v>2.2548</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2633</v>
+        <v>2.2548</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2633</v>
+        <v>2.2548</v>
       </c>
       <c r="I22" t="n">
         <v>2.2738</v>
@@ -1468,7 +1468,7 @@
         <v>1.3468</v>
       </c>
       <c r="D23" t="n">
-        <v>0.453</v>
+        <v>0.4184</v>
       </c>
       <c r="E23" t="n">
         <v>2.1644</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1575</v>
+        <v>2.1495</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3425</v>
+        <v>1.3375</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4502</v>
+        <v>0.4125</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1575</v>
+        <v>2.1495</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1575</v>
+        <v>2.1495</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1575</v>
+        <v>2.1495</v>
       </c>
       <c r="I24" t="n">
         <v>2.1676</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.1395</v>
+        <v>2.1316</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3313</v>
+        <v>1.3264</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4429</v>
+        <v>0.4053</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1395</v>
+        <v>2.1316</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1395</v>
+        <v>2.1316</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1395</v>
+        <v>2.1316</v>
       </c>
       <c r="I25" t="n">
         <v>2.1495</v>
@@ -1606,7 +1606,7 @@
         <v>1.3174</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4339</v>
+        <v>0.3995</v>
       </c>
       <c r="E26" t="n">
         <v>2.1171</v>
@@ -1652,7 +1652,7 @@
         <v>1.0943</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2891</v>
+        <v>0.2567</v>
       </c>
       <c r="E27" t="n">
         <v>1.7586</v>
@@ -1698,7 +1698,7 @@
         <v>1.09</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2863</v>
+        <v>0.254</v>
       </c>
       <c r="E28" t="n">
         <v>1.7517</v>
@@ -1744,7 +1744,7 @@
         <v>0.9764</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2125</v>
+        <v>0.1812</v>
       </c>
       <c r="E29" t="n">
         <v>1.5691</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.338</v>
+        <v>1.3313</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8326</v>
+        <v>0.8284</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1192</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>1.338</v>
+        <v>1.3313</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2961</v>
+        <v>1.3313</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0419</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2961</v>
+        <v>1.3313</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3082</v>
+        <v>1.3313</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0419</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>238</v>
+        <v>106</v>
       </c>
       <c r="L30" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3501</v>
+        <v>1.3313</v>
       </c>
       <c r="N30" t="n">
-        <v>428</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3313</v>
+        <v>1.3284</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8284</v>
+        <v>0.8266</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1165</v>
+        <v>0.0853</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3313</v>
+        <v>1.3284</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3313</v>
+        <v>1.2865</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.0419</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3313</v>
+        <v>1.2865</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3313</v>
+        <v>1.3082</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.0419</v>
       </c>
       <c r="K31" t="n">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3313</v>
+        <v>1.3501</v>
       </c>
       <c r="N31" t="n">
-        <v>106</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32">
@@ -1882,7 +1882,7 @@
         <v>0.8168</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1089</v>
+        <v>0.079</v>
       </c>
       <c r="E32" t="n">
         <v>1.3126</v>
@@ -1928,7 +1928,7 @@
         <v>0.7992</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0975</v>
+        <v>0.0678</v>
       </c>
       <c r="E33" t="n">
         <v>1.2843</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2039</v>
+        <v>1.1994</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7491</v>
+        <v>0.7463</v>
       </c>
       <c r="D34" t="n">
-        <v>0.065</v>
+        <v>0.0339</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2039</v>
+        <v>1.1994</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2039</v>
+        <v>1.1994</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2039</v>
+        <v>1.1994</v>
       </c>
       <c r="I34" t="n">
         <v>1.2095</v>
@@ -2020,7 +2020,7 @@
         <v>0.7325</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0542</v>
+        <v>0.025</v>
       </c>
       <c r="E35" t="n">
         <v>1.1771</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.1716</v>
+        <v>1.1663</v>
       </c>
       <c r="C36" t="n">
-        <v>0.729</v>
+        <v>0.7257</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0519</v>
+        <v>0.0207</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1716</v>
+        <v>1.1663</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7108</v>
+        <v>0.7055</v>
       </c>
       <c r="G36" t="n">
         <v>0.4608</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7108</v>
+        <v>0.7055</v>
       </c>
       <c r="I36" t="n">
         <v>0.7174</v>
@@ -2112,7 +2112,7 @@
         <v>0.6969</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0311</v>
+        <v>0.0023</v>
       </c>
       <c r="E37" t="n">
         <v>1.1199</v>
@@ -2158,7 +2158,7 @@
         <v>0.6729000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0155</v>
+        <v>-0.0131</v>
       </c>
       <c r="E38" t="n">
         <v>1.0814</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9656</v>
+        <v>0.9525</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6008</v>
+        <v>0.5927</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0313</v>
+        <v>-0.0644</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9656</v>
+        <v>0.9525</v>
       </c>
       <c r="F39" t="n">
-        <v>1.7633</v>
+        <v>1.7502</v>
       </c>
       <c r="G39" t="n">
         <v>-0.7977</v>
       </c>
       <c r="H39" t="n">
-        <v>1.7633</v>
+        <v>1.7502</v>
       </c>
       <c r="I39" t="n">
         <v>1.7798</v>
@@ -2250,7 +2250,7 @@
         <v>0.5919</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0371</v>
+        <v>-0.065</v>
       </c>
       <c r="E40" t="n">
         <v>0.9512</v>
@@ -2296,7 +2296,7 @@
         <v>0.5786</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0457</v>
+        <v>-0.0735</v>
       </c>
       <c r="E41" t="n">
         <v>0.9298</v>
@@ -2342,7 +2342,7 @@
         <v>0.5682</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0524</v>
+        <v>-0.0801</v>
       </c>
       <c r="E42" t="n">
         <v>0.9132</v>
@@ -2388,7 +2388,7 @@
         <v>0.4811</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.109</v>
+        <v>-0.1359</v>
       </c>
       <c r="E43" t="n">
         <v>0.7731</v>
@@ -2434,7 +2434,7 @@
         <v>0.4798</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1099</v>
+        <v>-0.1367</v>
       </c>
       <c r="E44" t="n">
         <v>0.771</v>
@@ -2480,7 +2480,7 @@
         <v>0.4056</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.158</v>
+        <v>-0.1842</v>
       </c>
       <c r="E45" t="n">
         <v>0.6518</v>
@@ -2526,7 +2526,7 @@
         <v>0.2856</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.236</v>
+        <v>-0.2611</v>
       </c>
       <c r="E46" t="n">
         <v>0.4589</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3023</v>
+        <v>0.301</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1881</v>
+        <v>0.1873</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2992</v>
+        <v>-0.324</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3023</v>
+        <v>0.301</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3432</v>
+        <v>0.3419</v>
       </c>
       <c r="G47" t="n">
         <v>-0.0409</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3432</v>
+        <v>0.3419</v>
       </c>
       <c r="I47" t="n">
         <v>0.3448</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2876</v>
+        <v>0.2903</v>
       </c>
       <c r="C48" t="n">
-        <v>0.179</v>
+        <v>0.1806</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3052</v>
+        <v>-0.3283</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2876</v>
+        <v>0.2903</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.3579</v>
+        <v>-0.3552</v>
       </c>
       <c r="G48" t="n">
         <v>0.6455</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.3579</v>
+        <v>-0.3552</v>
       </c>
       <c r="I48" t="n">
         <v>-0.3612</v>
@@ -2664,7 +2664,7 @@
         <v>0.1396</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3307</v>
+        <v>-0.3545</v>
       </c>
       <c r="E49" t="n">
         <v>0.2244</v>
@@ -2710,7 +2710,7 @@
         <v>0.0486</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3898</v>
+        <v>-0.4128</v>
       </c>
       <c r="E50" t="n">
         <v>0.0781</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0437</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4497</v>
+        <v>-0.4719</v>
       </c>
       <c r="E51" t="n">
         <v>-0.0702</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1347</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5088</v>
+        <v>-0.5301</v>
       </c>
       <c r="E52" t="n">
         <v>-0.2164</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1478</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5173</v>
+        <v>-0.5385</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2375</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1577</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5238</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2535</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1796</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.538</v>
+        <v>-0.5589</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2887</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2471</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5818</v>
+        <v>-0.6021</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3971</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2544</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5865</v>
+        <v>-0.6068</v>
       </c>
       <c r="E57" t="n">
         <v>-0.4088</v>
@@ -3078,7 +3078,7 @@
         <v>-0.3306</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.636</v>
+        <v>-0.6556</v>
       </c>
       <c r="E58" t="n">
         <v>-0.5313</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3892</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6741</v>
+        <v>-0.6931</v>
       </c>
       <c r="E59" t="n">
         <v>-0.6254999999999999</v>
@@ -3170,7 +3170,7 @@
         <v>-0.4622</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7214</v>
+        <v>-0.7398</v>
       </c>
       <c r="E60" t="n">
         <v>-0.7428</v>
@@ -3206,7 +3206,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3216,7 +3216,7 @@
         <v>-0.492</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7408</v>
+        <v>-0.7589</v>
       </c>
       <c r="E61" t="n">
         <v>-0.7907</v>
@@ -3231,68 +3231,68 @@
         <v>-0.7907</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7907</v>
+        <v>-0.7974</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7907</v>
+        <v>-0.7974</v>
       </c>
       <c r="N61" t="n">
-        <v>106</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7937</v>
+        <v>-0.7907</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4939</v>
+        <v>-0.492</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.742</v>
+        <v>-0.7589</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7937</v>
+        <v>-0.7907</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7937</v>
+        <v>-0.7907</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7937</v>
+        <v>-0.7907</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7974</v>
+        <v>-0.7907</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>234</v>
+        <v>106</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7974</v>
+        <v>-0.7907</v>
       </c>
       <c r="N62" t="n">
-        <v>234</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63">
@@ -3308,7 +3308,7 @@
         <v>-0.5317</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7665</v>
+        <v>-0.7843</v>
       </c>
       <c r="E63" t="n">
         <v>-0.8544</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5435</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7742</v>
+        <v>-0.7919</v>
       </c>
       <c r="E64" t="n">
         <v>-0.8734</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5775</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7963</v>
+        <v>-0.8137</v>
       </c>
       <c r="E65" t="n">
         <v>-0.9281</v>
@@ -3446,7 +3446,7 @@
         <v>-0.5793</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7975</v>
+        <v>-0.8148</v>
       </c>
       <c r="E66" t="n">
         <v>-0.931</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5953000000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8078</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9567</v>
@@ -3538,7 +3538,7 @@
         <v>-0.6073</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8156</v>
+        <v>-0.8327</v>
       </c>
       <c r="E68" t="n">
         <v>-0.976</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6094000000000001</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.8341</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9794</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6447000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8399</v>
+        <v>-0.8567</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0361</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6471</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8415</v>
+        <v>-0.8582</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0399</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6953</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8728</v>
+        <v>-0.8891</v>
       </c>
       <c r="E72" t="n">
         <v>-1.1174</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1306</v>
+        <v>-1.1299</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7035</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8781</v>
+        <v>-0.8941</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1306</v>
+        <v>-1.1299</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.1998</v>
+        <v>-0.1991</v>
       </c>
       <c r="G73" t="n">
         <v>-0.9308</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.1998</v>
+        <v>-0.1991</v>
       </c>
       <c r="I73" t="n">
         <v>-0.2008</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7573</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.913</v>
+        <v>-0.9288</v>
       </c>
       <c r="E74" t="n">
         <v>-1.2171</v>
@@ -3860,7 +3860,7 @@
         <v>-0.835</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9635</v>
+        <v>-0.9785</v>
       </c>
       <c r="E75" t="n">
         <v>-1.3419</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.7916</v>
+        <v>-1.7849</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.1148</v>
+        <v>-1.1107</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1451</v>
+        <v>-1.155</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.7916</v>
+        <v>-1.7849</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.7916</v>
+        <v>-1.7849</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.7916</v>
+        <v>-1.7849</v>
       </c>
       <c r="I76" t="n">
         <v>-1.7999</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1161</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.146</v>
+        <v>-1.1585</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7937</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.8375</v>
+        <v>-1.8247</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1434</v>
+        <v>-1.1354</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1637</v>
+        <v>-1.1709</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.8375</v>
+        <v>-1.8247</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.7138</v>
+        <v>-1.701</v>
       </c>
       <c r="G78" t="n">
         <v>-0.1237</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.7138</v>
+        <v>-1.701</v>
       </c>
       <c r="I78" t="n">
         <v>-1.7298</v>
@@ -4044,7 +4044,7 @@
         <v>-1.4588</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3684</v>
+        <v>-1.3779</v>
       </c>
       <c r="E79" t="n">
         <v>-2.3444</v>
@@ -4090,7 +4090,7 @@
         <v>-1.4834</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3844</v>
+        <v>-1.3937</v>
       </c>
       <c r="E80" t="n">
         <v>-2.3839</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.5974</v>
+        <v>-2.5877</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.6162</v>
+        <v>-1.6102</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4707</v>
+        <v>-1.4749</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.5974</v>
+        <v>-2.5877</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.5974</v>
+        <v>-2.5877</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.5974</v>
+        <v>-2.5877</v>
       </c>
       <c r="I81" t="n">
         <v>-2.6095</v>

--- a/database/event/8240/event_8240_evp_summary.xlsx
+++ b/database/event/8240/event_8240_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.6729</v>
+        <v>12.2246</v>
       </c>
       <c r="C2" t="n">
-        <v>7.2635</v>
+        <v>7.6068</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6895</v>
+        <v>4.8466</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6729</v>
+        <v>12.2246</v>
       </c>
       <c r="F2" t="n">
         <v>4.5807</v>
@@ -514,13 +514,13 @@
         <v>7.0923</v>
       </c>
       <c r="H2" t="n">
-        <v>11.7144</v>
+        <v>11.7359</v>
       </c>
       <c r="I2" t="n">
-        <v>6.3257</v>
+        <v>6.3373</v>
       </c>
       <c r="J2" t="n">
-        <v>7.357</v>
+        <v>7.3573</v>
       </c>
       <c r="K2" t="n">
         <v>144</v>
@@ -529,7 +529,7 @@
         <v>122</v>
       </c>
       <c r="M2" t="n">
-        <v>13.6827</v>
+        <v>13.6946</v>
       </c>
       <c r="N2" t="n">
         <v>266</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5258</v>
+        <v>6.9202</v>
       </c>
       <c r="C3" t="n">
-        <v>4.0607</v>
+        <v>4.3061</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3465</v>
+        <v>2.4773</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5258</v>
+        <v>6.9202</v>
       </c>
       <c r="F3" t="n">
         <v>4.5807</v>
@@ -560,10 +560,10 @@
         <v>1.9452</v>
       </c>
       <c r="H3" t="n">
-        <v>12.8662</v>
+        <v>12.8344</v>
       </c>
       <c r="I3" t="n">
-        <v>6.9476</v>
+        <v>6.9304</v>
       </c>
       <c r="J3" t="n">
         <v>1.9452</v>
@@ -575,7 +575,7 @@
         <v>70</v>
       </c>
       <c r="M3" t="n">
-        <v>8.892800000000001</v>
+        <v>8.8756</v>
       </c>
       <c r="N3" t="n">
         <v>274</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2683</v>
+        <v>6.427</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9005</v>
+        <v>3.9992</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2293</v>
+        <v>2.257</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2683</v>
+        <v>6.427</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8595</v>
+        <v>3.8596</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4087</v>
+        <v>2.4083</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7224</v>
+        <v>5.7225</v>
       </c>
       <c r="I4" t="n">
-        <v>6.0211</v>
+        <v>6.0212</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4087</v>
+        <v>2.4083</v>
       </c>
       <c r="K4" t="n">
         <v>238</v>
@@ -621,7 +621,7 @@
         <v>190</v>
       </c>
       <c r="M4" t="n">
-        <v>8.4298</v>
+        <v>8.429500000000001</v>
       </c>
       <c r="N4" t="n">
         <v>428</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.2261</v>
+        <v>6.376</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8742</v>
+        <v>3.9675</v>
       </c>
       <c r="D5" t="n">
-        <v>2.21</v>
+        <v>2.2342</v>
       </c>
       <c r="E5" t="n">
-        <v>6.2261</v>
+        <v>6.376</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7857</v>
+        <v>2.7766</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4404</v>
+        <v>3.44</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3721</v>
+        <v>3.3521</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5481</v>
+        <v>3.5271</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4404</v>
+        <v>3.44</v>
       </c>
       <c r="K5" t="n">
         <v>238</v>
@@ -667,7 +667,7 @@
         <v>190</v>
       </c>
       <c r="M5" t="n">
-        <v>6.9885</v>
+        <v>6.9671</v>
       </c>
       <c r="N5" t="n">
         <v>428</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0872</v>
+        <v>6.1784</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7878</v>
+        <v>3.8445</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1468</v>
+        <v>2.1459</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0872</v>
+        <v>6.1784</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7226</v>
+        <v>3.7058</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3646</v>
+        <v>2.365</v>
       </c>
       <c r="H6" t="n">
-        <v>7.3881</v>
+        <v>7.3327</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9895</v>
+        <v>3.9596</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3646</v>
+        <v>2.365</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>6.3541</v>
+        <v>6.3246</v>
       </c>
       <c r="N6" t="n">
         <v>266</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.3443</v>
+        <v>5.6458</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3255</v>
+        <v>3.5131</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8086</v>
+        <v>1.908</v>
       </c>
       <c r="E7" t="n">
-        <v>5.3443</v>
+        <v>5.6458</v>
       </c>
       <c r="F7" t="n">
-        <v>4.51</v>
+        <v>4.5104</v>
       </c>
       <c r="G7" t="n">
         <v>0.8343</v>
       </c>
       <c r="H7" t="n">
-        <v>9.985900000000001</v>
+        <v>9.987399999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3923</v>
+        <v>5.3931</v>
       </c>
       <c r="J7" t="n">
         <v>0.8343</v>
@@ -759,7 +759,7 @@
         <v>70</v>
       </c>
       <c r="M7" t="n">
-        <v>6.226599999999999</v>
+        <v>6.227399999999999</v>
       </c>
       <c r="N7" t="n">
         <v>274</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.2288</v>
+        <v>5.4013</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2536</v>
+        <v>3.361</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7561</v>
+        <v>1.7988</v>
       </c>
       <c r="E8" t="n">
-        <v>5.2288</v>
+        <v>5.4013</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3267</v>
+        <v>3.3265</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9021</v>
+        <v>1.9016</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5561</v>
+        <v>4.5558</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7939</v>
+        <v>4.7936</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9021</v>
+        <v>1.9016</v>
       </c>
       <c r="K8" t="n">
         <v>238</v>
@@ -805,7 +805,7 @@
         <v>190</v>
       </c>
       <c r="M8" t="n">
-        <v>6.696</v>
+        <v>6.6952</v>
       </c>
       <c r="N8" t="n">
         <v>428</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5568</v>
+        <v>4.5262</v>
       </c>
       <c r="C9" t="n">
-        <v>2.8355</v>
+        <v>2.8164</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4501</v>
+        <v>1.4079</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5568</v>
+        <v>4.5262</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9859</v>
+        <v>2.9858</v>
       </c>
       <c r="G9" t="n">
-        <v>1.571</v>
+        <v>1.5608</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9573</v>
+        <v>4.9571</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6769</v>
+        <v>2.6768</v>
       </c>
       <c r="J9" t="n">
-        <v>1.571</v>
+        <v>1.5608</v>
       </c>
       <c r="K9" t="n">
         <v>144</v>
@@ -851,7 +851,7 @@
         <v>122</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2479</v>
+        <v>4.2376</v>
       </c>
       <c r="N9" t="n">
         <v>266</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1262</v>
+        <v>4.3145</v>
       </c>
       <c r="C10" t="n">
-        <v>2.5675</v>
+        <v>2.6847</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2541</v>
+        <v>1.3134</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1262</v>
+        <v>4.3145</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1511</v>
+        <v>3.1532</v>
       </c>
       <c r="G10" t="n">
         <v>0.9751</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1718</v>
+        <v>4.1765</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3896</v>
+        <v>4.3946</v>
       </c>
       <c r="J10" t="n">
         <v>0.9751</v>
@@ -897,7 +897,7 @@
         <v>88</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3647</v>
+        <v>5.3697</v>
       </c>
       <c r="N10" t="n">
         <v>314</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0136</v>
+        <v>4.2621</v>
       </c>
       <c r="C11" t="n">
-        <v>2.4975</v>
+        <v>2.6521</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2029</v>
+        <v>1.29</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0136</v>
+        <v>4.2621</v>
       </c>
       <c r="F11" t="n">
         <v>4.0136</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4362</v>
+        <v>3.7511</v>
       </c>
       <c r="C12" t="n">
-        <v>2.1382</v>
+        <v>2.3341</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.0617</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4362</v>
+        <v>3.7511</v>
       </c>
       <c r="F12" t="n">
         <v>3.4362</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2696</v>
+        <v>3.6524</v>
       </c>
       <c r="C13" t="n">
-        <v>2.0345</v>
+        <v>2.2727</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8642</v>
+        <v>1.0176</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2696</v>
+        <v>3.6524</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7436</v>
+        <v>3.1421</v>
       </c>
       <c r="G13" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1581</v>
+        <v>4.1521</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2454</v>
+        <v>4.1521</v>
       </c>
       <c r="J13" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>204</v>
+        <v>113</v>
       </c>
       <c r="L13" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7714</v>
+        <v>4.1521</v>
       </c>
       <c r="N13" t="n">
-        <v>274</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.254</v>
+        <v>3.3544</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0248</v>
+        <v>2.0873</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8571</v>
+        <v>0.8845</v>
       </c>
       <c r="E14" t="n">
-        <v>3.254</v>
+        <v>3.3544</v>
       </c>
       <c r="F14" t="n">
         <v>2.6231</v>
@@ -1066,10 +1066,10 @@
         <v>0.6309</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0163</v>
+        <v>3.0161</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1738</v>
+        <v>3.1736</v>
       </c>
       <c r="J14" t="n">
         <v>0.6309</v>
@@ -1081,7 +1081,7 @@
         <v>88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8047</v>
+        <v>3.8045</v>
       </c>
       <c r="N14" t="n">
         <v>314</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.1827</v>
+        <v>3.2826</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9804</v>
+        <v>2.0426</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8246</v>
+        <v>0.8524</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1827</v>
+        <v>3.2826</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1828</v>
+        <v>2.7441</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9999</v>
+        <v>0.526</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3078</v>
+        <v>4.1596</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2462</v>
+        <v>2.2462</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9999</v>
+        <v>0.526</v>
       </c>
       <c r="K15" t="n">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="L15" t="n">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2461</v>
+        <v>2.7722</v>
       </c>
       <c r="N15" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.1312</v>
+        <v>3.195</v>
       </c>
       <c r="C16" t="n">
-        <v>1.9484</v>
+        <v>1.9881</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8012</v>
+        <v>0.8133</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1312</v>
+        <v>3.195</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1312</v>
+        <v>3.0459</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1283</v>
+        <v>3.9416</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1283</v>
+        <v>4.0432</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>113</v>
+        <v>249</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1283</v>
+        <v>4.0432</v>
       </c>
       <c r="N16" t="n">
-        <v>113</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.1174</v>
+        <v>3.1435</v>
       </c>
       <c r="C17" t="n">
-        <v>1.9398</v>
+        <v>1.9561</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7903</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1174</v>
+        <v>3.1435</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1174</v>
+        <v>3.1092</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.0981</v>
+        <v>4.0802</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2037</v>
+        <v>4.1853</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2037</v>
+        <v>4.1853</v>
       </c>
       <c r="N17" t="n">
         <v>249</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.0679</v>
+        <v>2.9903</v>
       </c>
       <c r="C18" t="n">
-        <v>1.909</v>
+        <v>1.8607</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7724</v>
+        <v>0.7219</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0679</v>
+        <v>2.9903</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6619</v>
+        <v>2.674</v>
       </c>
       <c r="G18" t="n">
-        <v>0.406</v>
+        <v>0.4061</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8884</v>
+        <v>3.9282</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0997</v>
+        <v>2.1212</v>
       </c>
       <c r="J18" t="n">
-        <v>0.406</v>
+        <v>0.4061</v>
       </c>
       <c r="K18" t="n">
         <v>144</v>
@@ -1265,7 +1265,7 @@
         <v>122</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5057</v>
+        <v>2.5273</v>
       </c>
       <c r="N18" t="n">
         <v>266</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0459</v>
+        <v>2.9071</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8953</v>
+        <v>1.809</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7624</v>
+        <v>0.6847</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0459</v>
+        <v>2.9071</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0459</v>
+        <v>2.1595</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.0002</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9416</v>
+        <v>2.231</v>
       </c>
       <c r="I19" t="n">
-        <v>4.0432</v>
+        <v>1.2047</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.0002</v>
       </c>
       <c r="K19" t="n">
-        <v>249</v>
+        <v>144</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M19" t="n">
-        <v>4.0432</v>
+        <v>2.2049</v>
       </c>
       <c r="N19" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.8342</v>
+        <v>2.8388</v>
       </c>
       <c r="C20" t="n">
-        <v>1.7636</v>
+        <v>1.7665</v>
       </c>
       <c r="D20" t="n">
-        <v>0.666</v>
+        <v>0.6542</v>
       </c>
       <c r="E20" t="n">
-        <v>2.8342</v>
+        <v>2.8388</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4597</v>
+        <v>2.4553</v>
       </c>
       <c r="G20" t="n">
         <v>0.3745</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6585</v>
+        <v>2.649</v>
       </c>
       <c r="I20" t="n">
-        <v>2.727</v>
+        <v>2.7173</v>
       </c>
       <c r="J20" t="n">
         <v>0.3745</v>
@@ -1357,7 +1357,7 @@
         <v>49</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1015</v>
+        <v>3.0918</v>
       </c>
       <c r="N20" t="n">
         <v>225</v>
@@ -1366,277 +1366,277 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7097</v>
+        <v>2.6996</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6861</v>
+        <v>1.6798</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6093</v>
+        <v>0.592</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7097</v>
+        <v>2.6996</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5592</v>
+        <v>2.678</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1505</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5495</v>
+        <v>3.1364</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9167</v>
+        <v>3.2172</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1505</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="L21" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0672</v>
+        <v>3.2172</v>
       </c>
       <c r="N21" t="n">
-        <v>274</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6779</v>
+        <v>2.5767</v>
       </c>
       <c r="C22" t="n">
-        <v>1.6663</v>
+        <v>1.6034</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5948</v>
+        <v>0.5371</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6779</v>
+        <v>2.5767</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6779</v>
+        <v>3.2003</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.718</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1362</v>
+        <v>4.2795</v>
       </c>
       <c r="I22" t="n">
-        <v>3.217</v>
+        <v>4.3898</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.718</v>
       </c>
       <c r="K22" t="n">
-        <v>249</v>
+        <v>176</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M22" t="n">
-        <v>3.217</v>
+        <v>3.6718</v>
       </c>
       <c r="N22" t="n">
-        <v>249</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.5977</v>
+        <v>2.5722</v>
       </c>
       <c r="C23" t="n">
-        <v>1.6164</v>
+        <v>1.6006</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5583</v>
+        <v>0.5351</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5977</v>
+        <v>2.5722</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5839</v>
+        <v>2.3362</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0138</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9304</v>
+        <v>2.3883</v>
       </c>
       <c r="I23" t="n">
-        <v>3.0059</v>
+        <v>2.3883</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0138</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="L23" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.0197</v>
+        <v>2.3883</v>
       </c>
       <c r="N23" t="n">
-        <v>225</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.482</v>
+        <v>2.5421</v>
       </c>
       <c r="C24" t="n">
-        <v>1.5444</v>
+        <v>1.5818</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5057</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.482</v>
+        <v>2.5421</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>2.5482</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.718</v>
+        <v>0.1505</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2789</v>
+        <v>3.5132</v>
       </c>
       <c r="I24" t="n">
-        <v>4.3892</v>
+        <v>1.8971</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.718</v>
+        <v>0.1505</v>
       </c>
       <c r="K24" t="n">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="L24" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6712</v>
+        <v>2.0476</v>
       </c>
       <c r="N24" t="n">
-        <v>225</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.4376</v>
+        <v>2.519</v>
       </c>
       <c r="C25" t="n">
-        <v>1.5168</v>
+        <v>1.5675</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4854</v>
+        <v>0.5114</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4376</v>
+        <v>2.519</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4376</v>
+        <v>2.5841</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.0138</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6101</v>
+        <v>2.9309</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6774</v>
+        <v>3.0064</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.0138</v>
       </c>
       <c r="K25" t="n">
-        <v>234</v>
+        <v>176</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M25" t="n">
-        <v>2.6774</v>
+        <v>3.0202</v>
       </c>
       <c r="N25" t="n">
-        <v>234</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.3317</v>
+        <v>2.3787</v>
       </c>
       <c r="C26" t="n">
-        <v>1.4509</v>
+        <v>1.4802</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4372</v>
+        <v>0.4487</v>
       </c>
       <c r="E26" t="n">
-        <v>2.3317</v>
+        <v>2.3787</v>
       </c>
       <c r="F26" t="n">
-        <v>2.3317</v>
+        <v>2.4376</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.3785</v>
+        <v>2.6101</v>
       </c>
       <c r="I26" t="n">
-        <v>2.3785</v>
+        <v>2.6774</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.3785</v>
+        <v>2.6774</v>
       </c>
       <c r="N26" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2591</v>
+        <v>2.3135</v>
       </c>
       <c r="C27" t="n">
-        <v>1.4057</v>
+        <v>1.4396</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4042</v>
+        <v>0.4196</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2591</v>
+        <v>2.3135</v>
       </c>
       <c r="F27" t="n">
-        <v>2.2591</v>
+        <v>2.2595</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2591</v>
+        <v>2.2595</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2591</v>
+        <v>2.2595</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.2591</v>
+        <v>2.2595</v>
       </c>
       <c r="N27" t="n">
         <v>184</v>
@@ -1688,507 +1688,507 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.0109</v>
+        <v>2.0184</v>
       </c>
       <c r="C28" t="n">
-        <v>1.2513</v>
+        <v>1.256</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2912</v>
+        <v>0.2878</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0109</v>
+        <v>2.0184</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2801</v>
+        <v>1.8859</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7308</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2801</v>
+        <v>1.8859</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3469</v>
+        <v>1.8859</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7308</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="L28" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.0777</v>
+        <v>1.8859</v>
       </c>
       <c r="N28" t="n">
-        <v>314</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8972</v>
+        <v>1.9718</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1805</v>
+        <v>1.227</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2394</v>
+        <v>0.2669</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8972</v>
+        <v>1.9718</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8972</v>
+        <v>1.2799</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.7308</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8972</v>
+        <v>1.2799</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8972</v>
+        <v>1.3467</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.7308</v>
       </c>
       <c r="K29" t="n">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M29" t="n">
-        <v>1.8972</v>
+        <v>2.0775</v>
       </c>
       <c r="N29" t="n">
-        <v>184</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.8792</v>
+        <v>1.9279</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1693</v>
+        <v>1.1996</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2312</v>
+        <v>0.2473</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8792</v>
+        <v>1.9279</v>
       </c>
       <c r="F30" t="n">
-        <v>2.6792</v>
+        <v>1.8294</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.1391</v>
+        <v>1.8294</v>
       </c>
       <c r="I30" t="n">
-        <v>3.1391</v>
+        <v>1.8765</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="L30" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.3391</v>
+        <v>1.8765</v>
       </c>
       <c r="N30" t="n">
-        <v>210</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.8291</v>
+        <v>1.7834</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1382</v>
+        <v>1.1097</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2084</v>
+        <v>0.1828</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8291</v>
+        <v>1.7834</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8291</v>
+        <v>2.6793</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8291</v>
+        <v>3.1393</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8762</v>
+        <v>3.1393</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>249</v>
+        <v>173</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M31" t="n">
-        <v>1.8762</v>
+        <v>2.3393</v>
       </c>
       <c r="N31" t="n">
-        <v>249</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.7009</v>
+        <v>1.7817</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0584</v>
+        <v>1.1087</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1501</v>
+        <v>0.182</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7009</v>
+        <v>1.7817</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7009</v>
+        <v>1.6949</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7009</v>
+        <v>1.6949</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7009</v>
+        <v>1.6949</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.7009</v>
+        <v>1.6949</v>
       </c>
       <c r="N32" t="n">
-        <v>168</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.6949</v>
+        <v>1.7379</v>
       </c>
       <c r="C33" t="n">
-        <v>1.0547</v>
+        <v>1.0814</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1474</v>
+        <v>0.1625</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6949</v>
+        <v>1.7379</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6949</v>
+        <v>1.3654</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6949</v>
+        <v>1.3654</v>
       </c>
       <c r="I33" t="n">
-        <v>1.6949</v>
+        <v>1.3654</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.6949</v>
+        <v>1.3654</v>
       </c>
       <c r="N33" t="n">
-        <v>106</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.6308</v>
+        <v>1.6851</v>
       </c>
       <c r="C34" t="n">
-        <v>1.0148</v>
+        <v>1.0486</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1182</v>
+        <v>0.1389</v>
       </c>
       <c r="E34" t="n">
-        <v>1.6308</v>
+        <v>1.6851</v>
       </c>
       <c r="F34" t="n">
-        <v>1.5939</v>
+        <v>1.7406</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0369</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5939</v>
+        <v>1.7406</v>
       </c>
       <c r="I34" t="n">
-        <v>1.6771</v>
+        <v>1.7406</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0369</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="L34" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.714</v>
+        <v>1.7406</v>
       </c>
       <c r="N34" t="n">
-        <v>428</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.4127</v>
+        <v>1.668</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8791</v>
+        <v>1.0379</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0189</v>
+        <v>0.1312</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4127</v>
+        <v>1.668</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8603</v>
+        <v>1.3411</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.4476</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.8603</v>
+        <v>1.3411</v>
       </c>
       <c r="I35" t="n">
-        <v>1.9574</v>
+        <v>1.3411</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4476</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="L35" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.5098</v>
+        <v>1.3411</v>
       </c>
       <c r="N35" t="n">
-        <v>314</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.3938</v>
+        <v>1.5145</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8673</v>
+        <v>0.9424</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0103</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>1.3938</v>
+        <v>1.5145</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3938</v>
+        <v>1.8648</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.4476</v>
       </c>
       <c r="H36" t="n">
-        <v>1.3938</v>
+        <v>1.8648</v>
       </c>
       <c r="I36" t="n">
-        <v>1.3938</v>
+        <v>1.9622</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.4476</v>
       </c>
       <c r="K36" t="n">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M36" t="n">
-        <v>1.3938</v>
+        <v>1.5146</v>
       </c>
       <c r="N36" t="n">
-        <v>128</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.3654</v>
+        <v>1.4814</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8496</v>
+        <v>0.9218</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0026</v>
+        <v>0.0479</v>
       </c>
       <c r="E37" t="n">
-        <v>1.3654</v>
+        <v>1.4814</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3654</v>
+        <v>1.3928</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.3654</v>
+        <v>1.3928</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3654</v>
+        <v>1.3928</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.3654</v>
+        <v>1.3928</v>
       </c>
       <c r="N37" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3501</v>
+        <v>1.4316</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8401</v>
+        <v>0.8908</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0256</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3501</v>
+        <v>1.4316</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3501</v>
+        <v>1.6056</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.0369</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3501</v>
+        <v>1.6056</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3501</v>
+        <v>1.6894</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.0369</v>
       </c>
       <c r="K38" t="n">
-        <v>95</v>
+        <v>238</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3501</v>
+        <v>1.7263</v>
       </c>
       <c r="N38" t="n">
-        <v>95</v>
+        <v>428</v>
       </c>
     </row>
     <row r="39">
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.2345</v>
+        <v>1.4016</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7682</v>
+        <v>0.8722</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0622</v>
+        <v>0.0122</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2345</v>
+        <v>1.4016</v>
       </c>
       <c r="F39" t="n">
         <v>1.2345</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.2123</v>
+        <v>1.3951</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7544</v>
+        <v>0.8681</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0723</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>1.2123</v>
+        <v>1.3951</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2123</v>
+        <v>1.2347</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2123</v>
+        <v>1.2347</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2123</v>
+        <v>1.2347</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.2123</v>
+        <v>1.2347</v>
       </c>
       <c r="N40" t="n">
         <v>184</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.1901</v>
+        <v>1.3785</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7405</v>
+        <v>0.8578</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0824</v>
+        <v>0.0019</v>
       </c>
       <c r="E41" t="n">
-        <v>1.1901</v>
+        <v>1.3785</v>
       </c>
       <c r="F41" t="n">
-        <v>1.1901</v>
+        <v>1.1894</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1901</v>
+        <v>1.1894</v>
       </c>
       <c r="I41" t="n">
-        <v>1.1901</v>
+        <v>1.1894</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.1901</v>
+        <v>1.1894</v>
       </c>
       <c r="N41" t="n">
         <v>168</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.0905</v>
+        <v>1.2122</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6786</v>
+        <v>0.7543</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1278</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>1.0905</v>
+        <v>1.2122</v>
       </c>
       <c r="F42" t="n">
-        <v>1.0905</v>
+        <v>1.0904</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0905</v>
+        <v>1.0904</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0905</v>
+        <v>1.0904</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.0905</v>
+        <v>1.0904</v>
       </c>
       <c r="N42" t="n">
         <v>128</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.0791</v>
+        <v>1.1212</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6715</v>
+        <v>0.6977</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.133</v>
+        <v>-0.113</v>
       </c>
       <c r="E43" t="n">
-        <v>1.0791</v>
+        <v>1.1212</v>
       </c>
       <c r="F43" t="n">
-        <v>0.949</v>
+        <v>0.9492</v>
       </c>
       <c r="G43" t="n">
         <v>0.1301</v>
       </c>
       <c r="H43" t="n">
-        <v>0.949</v>
+        <v>0.9492</v>
       </c>
       <c r="I43" t="n">
-        <v>0.949</v>
+        <v>0.9492</v>
       </c>
       <c r="J43" t="n">
         <v>0.1301</v>
@@ -2415,7 +2415,7 @@
         <v>37</v>
       </c>
       <c r="M43" t="n">
-        <v>1.0791</v>
+        <v>1.0793</v>
       </c>
       <c r="N43" t="n">
         <v>210</v>
@@ -2424,185 +2424,185 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.0596</v>
+        <v>1.0624</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6593</v>
+        <v>0.6611</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1419</v>
+        <v>-0.1393</v>
       </c>
       <c r="E44" t="n">
-        <v>1.0596</v>
+        <v>1.0624</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0596</v>
+        <v>1.0025</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.0596</v>
+        <v>1.0025</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0596</v>
+        <v>1.0025</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.0596</v>
+        <v>1.0025</v>
       </c>
       <c r="N44" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.0024</v>
+        <v>1.0576</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6237</v>
+        <v>0.6581</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1679</v>
+        <v>-0.1414</v>
       </c>
       <c r="E45" t="n">
-        <v>1.0024</v>
+        <v>1.0576</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0024</v>
+        <v>0.8633</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.1254</v>
       </c>
       <c r="H45" t="n">
-        <v>1.0024</v>
+        <v>0.8633</v>
       </c>
       <c r="I45" t="n">
-        <v>1.0024</v>
+        <v>0.8855</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.1254</v>
       </c>
       <c r="K45" t="n">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M45" t="n">
-        <v>1.0024</v>
+        <v>1.0109</v>
       </c>
       <c r="N45" t="n">
-        <v>108</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9941</v>
+        <v>1.0347</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6186</v>
+        <v>0.6438</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1717</v>
+        <v>-0.1516</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9941</v>
+        <v>1.0347</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9941</v>
+        <v>1.0697</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9941</v>
+        <v>1.0697</v>
       </c>
       <c r="I46" t="n">
-        <v>0.9941</v>
+        <v>1.0697</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9941</v>
+        <v>1.0697</v>
       </c>
       <c r="N46" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9963</v>
       </c>
       <c r="C47" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1743</v>
+        <v>-0.1688</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9963</v>
       </c>
       <c r="F47" t="n">
-        <v>0.863</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1254</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.863</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8852</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1254</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="L47" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.0106</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>225</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48">
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.912</v>
+        <v>0.9175</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5675</v>
+        <v>0.5709</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.209</v>
+        <v>-0.204</v>
       </c>
       <c r="E48" t="n">
-        <v>0.912</v>
+        <v>0.9175</v>
       </c>
       <c r="F48" t="n">
-        <v>0.912</v>
+        <v>0.9112</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.912</v>
+        <v>0.9112</v>
       </c>
       <c r="I48" t="n">
-        <v>0.912</v>
+        <v>0.9112</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.912</v>
+        <v>0.9112</v>
       </c>
       <c r="N48" t="n">
         <v>168</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8519</v>
+        <v>0.8622</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5301</v>
+        <v>0.5365</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2364</v>
+        <v>-0.2287</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8519</v>
+        <v>0.8622</v>
       </c>
       <c r="F49" t="n">
-        <v>1.2491</v>
+        <v>1.2493</v>
       </c>
       <c r="G49" t="n">
         <v>-0.3972</v>
       </c>
       <c r="H49" t="n">
-        <v>1.2491</v>
+        <v>1.2493</v>
       </c>
       <c r="I49" t="n">
-        <v>1.2491</v>
+        <v>1.2493</v>
       </c>
       <c r="J49" t="n">
         <v>-0.3972</v>
@@ -2691,7 +2691,7 @@
         <v>37</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8519000000000001</v>
+        <v>0.8521000000000001</v>
       </c>
       <c r="N49" t="n">
         <v>210</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6947</v>
+        <v>0.5289</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4323</v>
+        <v>0.3291</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.308</v>
+        <v>-0.3776</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6947</v>
+        <v>0.5289</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1343</v>
+        <v>0.134</v>
       </c>
       <c r="G50" t="n">
         <v>0.5604</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1343</v>
+        <v>0.134</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1413</v>
+        <v>0.141</v>
       </c>
       <c r="J50" t="n">
         <v>0.5604</v>
@@ -2737,7 +2737,7 @@
         <v>88</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7017</v>
+        <v>0.7014</v>
       </c>
       <c r="N50" t="n">
         <v>314</v>
@@ -2750,16 +2750,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5206</v>
+        <v>0.5042</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3239</v>
+        <v>0.3137</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3872</v>
+        <v>-0.3886</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5206</v>
+        <v>0.5042</v>
       </c>
       <c r="F51" t="n">
         <v>0.5206</v>
@@ -2792,93 +2792,93 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>krazy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3192</v>
+        <v>0.3105</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1986</v>
+        <v>0.1932</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4789</v>
+        <v>-0.4751</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3192</v>
+        <v>0.3105</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3192</v>
+        <v>0.1766</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3192</v>
+        <v>0.1766</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3192</v>
+        <v>0.1766</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3192</v>
+        <v>0.1766</v>
       </c>
       <c r="N52" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>krazy</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.1766</v>
+        <v>0.3045</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1099</v>
+        <v>0.1895</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5438</v>
+        <v>-0.4778</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1766</v>
+        <v>0.3045</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1766</v>
+        <v>0.3185</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1766</v>
+        <v>0.3185</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1766</v>
+        <v>0.3185</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1766</v>
+        <v>0.3185</v>
       </c>
       <c r="N53" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1748</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1088</v>
+        <v>0.0605</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5446</v>
+        <v>-0.5704</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1748</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1748</v>
+        <v>0.1754</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1748</v>
+        <v>0.1754</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1748</v>
+        <v>0.1754</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1748</v>
+        <v>0.1754</v>
       </c>
       <c r="N54" t="n">
         <v>108</v>
@@ -2930,47 +2930,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>Jeorge</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0083</v>
+        <v>-0.0806</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0052</v>
+        <v>-0.0502</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6204</v>
+        <v>-0.6498</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0083</v>
+        <v>-0.0806</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0083</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0083</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0083</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.0083</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0302</v>
+        <v>-0.1279</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0188</v>
+        <v>-0.0796</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.638</v>
+        <v>-0.671</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0302</v>
+        <v>-0.1279</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0302</v>
+        <v>-0.0306</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.0302</v>
+        <v>-0.0306</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0302</v>
+        <v>-0.0306</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.0302</v>
+        <v>-0.0306</v>
       </c>
       <c r="N56" t="n">
         <v>113</v>
@@ -3022,231 +3022,231 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jeorge</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.0692</v>
+        <v>-0.1324</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0431</v>
+        <v>-0.0824</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.673</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0692</v>
+        <v>-0.1324</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.0692</v>
+        <v>-0.0074</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.0692</v>
+        <v>-0.0074</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0692</v>
+        <v>-0.0074</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.0692</v>
+        <v>-0.0074</v>
       </c>
       <c r="N57" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1562</v>
+        <v>-0.4564</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.284</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6953</v>
+        <v>-0.8177</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1562</v>
+        <v>-0.4564</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4771</v>
+        <v>-0.6192</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.6333</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4771</v>
+        <v>-0.6192</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4894</v>
+        <v>-0.6192</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.6333</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>176</v>
+        <v>106</v>
       </c>
       <c r="L58" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1439</v>
+        <v>-0.6192</v>
       </c>
       <c r="N58" t="n">
-        <v>225</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.1614</v>
+        <v>-0.4578</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1004</v>
+        <v>-0.2849</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6977</v>
+        <v>-0.8183</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1614</v>
+        <v>-0.4578</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1614</v>
+        <v>0.4775</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-0.6333</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1614</v>
+        <v>0.4775</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1614</v>
+        <v>0.4898</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-0.6333</v>
       </c>
       <c r="K59" t="n">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.1614</v>
+        <v>-0.1435</v>
       </c>
       <c r="N59" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.237</v>
+        <v>-0.4597</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1475</v>
+        <v>-0.286</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7321</v>
+        <v>-0.8192</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.237</v>
+        <v>-0.4597</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.237</v>
+        <v>-0.145</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.237</v>
+        <v>-0.145</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.237</v>
+        <v>-0.145</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.237</v>
+        <v>-0.145</v>
       </c>
       <c r="N60" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2371</v>
+        <v>-0.4771</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1475</v>
+        <v>-0.2969</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7321</v>
+        <v>-0.8269</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2371</v>
+        <v>-0.4771</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7629</v>
+        <v>-0.237</v>
       </c>
       <c r="G61" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.7629</v>
+        <v>-0.237</v>
       </c>
       <c r="I61" t="n">
-        <v>0.412</v>
+        <v>-0.237</v>
       </c>
       <c r="J61" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>204</v>
+        <v>150</v>
       </c>
       <c r="L61" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5880000000000001</v>
+        <v>-0.237</v>
       </c>
       <c r="N61" t="n">
-        <v>274</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62">
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2777</v>
+        <v>-0.4803</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1728</v>
+        <v>-0.2989</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7506</v>
+        <v>-0.8284</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2777</v>
+        <v>-0.4803</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2777</v>
+        <v>-0.2999</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2777</v>
+        <v>-0.2999</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2777</v>
+        <v>-0.2999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2777</v>
+        <v>-0.2999</v>
       </c>
       <c r="N62" t="n">
         <v>95</v>
@@ -3298,47 +3298,47 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3373</v>
+        <v>-0.4844</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2099</v>
+        <v>-0.3014</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.8302</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3373</v>
+        <v>-0.4844</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3373</v>
+        <v>0.7645</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3373</v>
+        <v>0.7645</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.346</v>
+        <v>0.4128</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K63" t="n">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.346</v>
+        <v>-0.5871999999999999</v>
       </c>
       <c r="N63" t="n">
-        <v>234</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3483</v>
+        <v>-0.489</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2167</v>
+        <v>-0.3043</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3483</v>
+        <v>-0.489</v>
       </c>
       <c r="F64" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0717</v>
       </c>
       <c r="G64" t="n">
         <v>-0.4294</v>
       </c>
       <c r="H64" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0717</v>
       </c>
       <c r="I64" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0717</v>
       </c>
       <c r="J64" t="n">
         <v>-0.4294</v>
@@ -3381,7 +3381,7 @@
         <v>37</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3483</v>
+        <v>-0.3577</v>
       </c>
       <c r="N64" t="n">
         <v>210</v>
@@ -3390,93 +3390,93 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3793</v>
+        <v>-0.4993</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.236</v>
+        <v>-0.3107</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.8368</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3793</v>
+        <v>-0.4993</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8545</v>
+        <v>-0.4606</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4752</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8545</v>
+        <v>-0.4606</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8991</v>
+        <v>-0.4606</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4752</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="L65" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.4239</v>
+        <v>-0.4606</v>
       </c>
       <c r="N65" t="n">
-        <v>428</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4516</v>
+        <v>-0.5058</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.281</v>
+        <v>-0.3147</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8298</v>
+        <v>-0.8398</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4516</v>
+        <v>-0.5058</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4516</v>
+        <v>-0.8125</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.4748</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4516</v>
+        <v>-0.8125</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4516</v>
+        <v>-0.8549</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>0.4748</v>
       </c>
       <c r="K66" t="n">
-        <v>108</v>
+        <v>238</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4516</v>
+        <v>-0.3801</v>
       </c>
       <c r="N66" t="n">
-        <v>108</v>
+        <v>428</v>
       </c>
     </row>
     <row r="67">
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.4696</v>
+        <v>-0.5077</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2922</v>
+        <v>-0.3159</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.838</v>
+        <v>-0.8406</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.4696</v>
+        <v>-0.5077</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.4696</v>
+        <v>-0.469</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.4696</v>
+        <v>-0.469</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.4696</v>
+        <v>-0.469</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.4696</v>
+        <v>-0.469</v>
       </c>
       <c r="N67" t="n">
         <v>108</v>
@@ -3528,124 +3528,124 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.481</v>
+        <v>-0.6286</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2993</v>
+        <v>-0.3911</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8946</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.481</v>
+        <v>-0.6286</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.481</v>
+        <v>-0.3373</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.481</v>
+        <v>-0.3373</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.481</v>
+        <v>-0.346</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>113</v>
+        <v>234</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.481</v>
+        <v>-0.346</v>
       </c>
       <c r="N68" t="n">
-        <v>113</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.6056</v>
+        <v>-0.6397</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3768</v>
+        <v>-0.3981</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8999</v>
+        <v>-0.8996</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.6056</v>
+        <v>-0.6397</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.6056</v>
+        <v>-0.4817</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.6056</v>
+        <v>-0.4817</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6056</v>
+        <v>-0.4817</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6056</v>
+        <v>-0.4817</v>
       </c>
       <c r="N69" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6192</v>
+        <v>-0.6771</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3853</v>
+        <v>-0.4213</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9061</v>
+        <v>-0.9163</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6192</v>
+        <v>-0.6771</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6192</v>
+        <v>-0.6424</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6192</v>
+        <v>-0.6424</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6192</v>
+        <v>-0.6424</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6192</v>
+        <v>-0.6424</v>
       </c>
       <c r="N70" t="n">
         <v>106</v>
@@ -3666,32 +3666,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6424</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3997</v>
+        <v>-0.472</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9166</v>
+        <v>-0.9527</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6424</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6424</v>
+        <v>-0.6851</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6424</v>
+        <v>-0.6851</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6424</v>
+        <v>-0.6851</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6424</v>
+        <v>-0.6851</v>
       </c>
       <c r="N71" t="n">
         <v>106</v>
@@ -3712,277 +3712,277 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6851</v>
+        <v>-0.7946</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4263</v>
+        <v>-0.4944</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9361</v>
+        <v>-0.9688</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6851</v>
+        <v>-0.7946</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6851</v>
+        <v>-0.6057</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6851</v>
+        <v>-0.6057</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6851</v>
+        <v>-0.6057</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6851</v>
+        <v>-0.6057</v>
       </c>
       <c r="N72" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>aragornN</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7579</v>
+        <v>-1.1201</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4716</v>
+        <v>-0.697</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9692</v>
+        <v>-1.1141</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7579</v>
+        <v>-1.1201</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7579</v>
+        <v>-0.965</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7579</v>
+        <v>-0.965</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7579</v>
+        <v>-0.965</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7579</v>
+        <v>-0.965</v>
       </c>
       <c r="N73" t="n">
-        <v>95</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8246</v>
+        <v>-1.1289</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5131</v>
+        <v>-0.7025</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9996</v>
+        <v>-1.1181</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.8246</v>
+        <v>-1.1289</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.8246</v>
+        <v>-0.249</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>-0.8159</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.8246</v>
+        <v>-0.249</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.8246</v>
+        <v>-0.249</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>-0.8159</v>
       </c>
       <c r="K74" t="n">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.8246</v>
+        <v>-1.0649</v>
       </c>
       <c r="N74" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9403</v>
+        <v>-1.1581</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5851</v>
+        <v>-0.7206</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0522</v>
+        <v>-1.1311</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9403</v>
+        <v>-1.1581</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.9403</v>
+        <v>-0.9635</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.9403</v>
+        <v>-0.9635</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.9403</v>
+        <v>-0.9635</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>168</v>
+        <v>106</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.9403</v>
+        <v>-0.9635</v>
       </c>
       <c r="N75" t="n">
-        <v>168</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.9635</v>
+        <v>-1.1835</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.5995</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0628</v>
+        <v>-1.1425</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9635</v>
+        <v>-1.1835</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.9635</v>
+        <v>-0.8246</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.9635</v>
+        <v>-0.8246</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9635</v>
+        <v>-0.8246</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.9635</v>
+        <v>-0.8246</v>
       </c>
       <c r="N76" t="n">
-        <v>106</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>aragornN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.0651</v>
+        <v>-1.2116</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.7539</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1091</v>
+        <v>-1.155</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.0651</v>
+        <v>-1.2116</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.2492</v>
+        <v>-0.7578</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.8159</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.2492</v>
+        <v>-0.7578</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.2492</v>
+        <v>-0.7578</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.8159</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>173</v>
+        <v>95</v>
       </c>
       <c r="L77" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.0651</v>
+        <v>-0.7578</v>
       </c>
       <c r="N77" t="n">
-        <v>210</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78">
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.0652</v>
+        <v>-1.3304</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.8278</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1091</v>
+        <v>-1.2081</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.0652</v>
+        <v>-1.3304</v>
       </c>
       <c r="F78" t="n">
         <v>-1.0652</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.5643</v>
+        <v>-1.649</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.9734</v>
+        <v>-1.0261</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3363</v>
+        <v>-1.3504</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.5643</v>
+        <v>-1.649</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.5643</v>
+        <v>-1.5639</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.5643</v>
+        <v>-1.5639</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.5643</v>
+        <v>-1.5639</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.5643</v>
+        <v>-1.5639</v>
       </c>
       <c r="N79" t="n">
         <v>184</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.7829</v>
+        <v>-2.0045</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.1094</v>
+        <v>-1.2473</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4358</v>
+        <v>-1.5092</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.7829</v>
+        <v>-2.0045</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.7829</v>
+        <v>-1.7827</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.7829</v>
+        <v>-1.7827</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.8288</v>
+        <v>-1.8286</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.8288</v>
+        <v>-1.8286</v>
       </c>
       <c r="N80" t="n">
         <v>249</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.849</v>
+        <v>-2.1853</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.1505</v>
+        <v>-1.3598</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4659</v>
+        <v>-1.5899</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.849</v>
+        <v>-2.1853</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.849</v>
+        <v>-1.8484</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.849</v>
+        <v>-1.8484</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.849</v>
+        <v>-1.8484</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.849</v>
+        <v>-1.8484</v>
       </c>
       <c r="N81" t="n">
         <v>184</v>
@@ -6466,13 +6466,13 @@
         <v>16</v>
       </c>
       <c r="H57" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.196</v>
+        <v>-0.1861</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.136</v>
+        <v>-2.9776</v>
       </c>
     </row>
     <row r="58">
@@ -6506,13 +6506,13 @@
         <v>16</v>
       </c>
       <c r="H58" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.248</v>
+        <v>-0.2386</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.968</v>
+        <v>-3.8176</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.74</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2775</v>
+        <v>-0.2781</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.44</v>
+        <v>-4.4496</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.65</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3583</v>
+        <v>-0.3587</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.7328</v>
+        <v>-5.7392</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.38</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5952</v>
+        <v>-0.5956</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.523199999999999</v>
+        <v>-9.5296</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.68</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1728</v>
+        <v>1.1732</v>
       </c>
       <c r="J62" t="n">
-        <v>23.456</v>
+        <v>23.464</v>
       </c>
     </row>
     <row r="63">
@@ -6706,13 +6706,13 @@
         <v>20</v>
       </c>
       <c r="H63" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1728</v>
+        <v>1.1604</v>
       </c>
       <c r="J63" t="n">
-        <v>23.456</v>
+        <v>23.208</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.32</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6887</v>
+        <v>0.6888</v>
       </c>
       <c r="J64" t="n">
-        <v>13.774</v>
+        <v>13.776</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1525</v>
+        <v>-0.1521</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.05</v>
+        <v>-3.042</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.86</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4996</v>
+        <v>-0.4993</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.992000000000001</v>
+        <v>-9.986000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -7669,10 +7669,10 @@
         <v>1.44</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9152</v>
       </c>
       <c r="J87" t="n">
-        <v>26.5582</v>
+        <v>26.5408</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.19</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5245</v>
+        <v>0.5241</v>
       </c>
       <c r="J88" t="n">
-        <v>15.2105</v>
+        <v>15.1989</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2811</v>
+        <v>0.2807</v>
       </c>
       <c r="J89" t="n">
-        <v>8.151899999999999</v>
+        <v>8.1403</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5238</v>
+        <v>-0.5242</v>
       </c>
       <c r="J90" t="n">
-        <v>-15.1902</v>
+        <v>-15.2018</v>
       </c>
     </row>
     <row r="91">
@@ -7826,13 +7826,13 @@
         <v>29</v>
       </c>
       <c r="H91" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.9826</v>
+        <v>-0.9625</v>
       </c>
       <c r="J91" t="n">
-        <v>-28.4954</v>
+        <v>-27.9125</v>
       </c>
     </row>
     <row r="92">
@@ -11466,13 +11466,13 @@
         <v>20</v>
       </c>
       <c r="H182" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="I182" t="n">
-        <v>1.8231</v>
+        <v>1.8343</v>
       </c>
       <c r="J182" t="n">
-        <v>36.462</v>
+        <v>36.686</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.56</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1577</v>
+        <v>1.1574</v>
       </c>
       <c r="J183" t="n">
-        <v>23.154</v>
+        <v>23.148</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.15</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4115</v>
+        <v>0.4111</v>
       </c>
       <c r="J184" t="n">
-        <v>8.23</v>
+        <v>8.222</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.15</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4115</v>
+        <v>0.4111</v>
       </c>
       <c r="J185" t="n">
-        <v>8.23</v>
+        <v>8.222</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7369</v>
+        <v>-0.7371</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.738</v>
+        <v>-14.742</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>0.9</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1322</v>
+        <v>-0.132</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.644</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>0.84</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1971</v>
+        <v>-0.1969</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.942</v>
+        <v>-3.938</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.84</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1971</v>
+        <v>-0.1969</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.942</v>
+        <v>-3.938</v>
       </c>
     </row>
     <row r="190">
@@ -11786,13 +11786,13 @@
         <v>20</v>
       </c>
       <c r="H190" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2549</v>
+        <v>-0.2643</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.098</v>
+        <v>-5.286</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2834</v>
+        <v>-0.2832</v>
       </c>
       <c r="J191" t="n">
-        <v>-5.668</v>
+        <v>-5.664</v>
       </c>
     </row>
     <row r="192">
@@ -11866,13 +11866,13 @@
         <v>21</v>
       </c>
       <c r="H192" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5856</v>
+        <v>0.6012</v>
       </c>
       <c r="J192" t="n">
-        <v>12.2976</v>
+        <v>12.6252</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.05</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1595</v>
+        <v>0.1591</v>
       </c>
       <c r="J193" t="n">
-        <v>3.3495</v>
+        <v>3.3411</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1186</v>
+        <v>-0.1187</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.4906</v>
+        <v>-2.4927</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2363</v>
+        <v>-0.2365</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.9623</v>
+        <v>-4.9665</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.61</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4227</v>
+        <v>-0.4229</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.8767</v>
+        <v>-8.8809</v>
       </c>
     </row>
     <row r="197">
@@ -12269,10 +12269,10 @@
         <v>1.57</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6824</v>
+        <v>0.6821</v>
       </c>
       <c r="J202" t="n">
-        <v>14.3304</v>
+        <v>14.3241</v>
       </c>
     </row>
     <row r="203">
@@ -12306,13 +12306,13 @@
         <v>21</v>
       </c>
       <c r="H203" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6131</v>
+        <v>0.6229</v>
       </c>
       <c r="J203" t="n">
-        <v>12.8751</v>
+        <v>13.0809</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.24</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3404</v>
+        <v>0.3403</v>
       </c>
       <c r="J204" t="n">
-        <v>7.1484</v>
+        <v>7.1463</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.16</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2438</v>
+        <v>0.2436</v>
       </c>
       <c r="J205" t="n">
-        <v>5.1198</v>
+        <v>5.1156</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.95</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1081</v>
+        <v>-0.1082</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.2701</v>
+        <v>-2.2722</v>
       </c>
     </row>
     <row r="207">
@@ -12866,13 +12866,13 @@
         <v>29</v>
       </c>
       <c r="H217" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9737</v>
+        <v>0.956</v>
       </c>
       <c r="J217" t="n">
-        <v>28.2373</v>
+        <v>27.724</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.21</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5819</v>
+        <v>0.5823</v>
       </c>
       <c r="J218" t="n">
-        <v>16.8751</v>
+        <v>16.8867</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.13</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3974</v>
+        <v>0.3976</v>
       </c>
       <c r="J219" t="n">
-        <v>11.5246</v>
+        <v>11.5304</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.98</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1179</v>
+        <v>-0.1175</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.4191</v>
+        <v>-3.4075</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5855</v>
+        <v>-0.5851</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.9795</v>
+        <v>-16.9679</v>
       </c>
     </row>
     <row r="222">
@@ -13266,13 +13266,13 @@
         <v>21</v>
       </c>
       <c r="H227" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4859</v>
+        <v>0.4981</v>
       </c>
       <c r="J227" t="n">
-        <v>10.2039</v>
+        <v>10.4601</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.25</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4336</v>
+        <v>0.433</v>
       </c>
       <c r="J228" t="n">
-        <v>9.105600000000001</v>
+        <v>9.093</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>0.75</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2898</v>
+        <v>-0.29</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.0858</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.66</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3731</v>
+        <v>-0.3734</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.8351</v>
+        <v>-7.8414</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.47</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5392</v>
+        <v>-0.5394</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.3232</v>
+        <v>-11.3274</v>
       </c>
     </row>
     <row r="232">
@@ -14469,10 +14469,10 @@
         <v>1.39</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8022</v>
+        <v>0.8012</v>
       </c>
       <c r="J257" t="n">
-        <v>14.4396</v>
+        <v>14.4216</v>
       </c>
     </row>
     <row r="258">
@@ -14506,13 +14506,13 @@
         <v>18</v>
       </c>
       <c r="H258" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1781</v>
+        <v>-0.1677</v>
       </c>
       <c r="J258" t="n">
-        <v>-3.2058</v>
+        <v>-3.0186</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1883</v>
+        <v>-0.1884</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.3894</v>
+        <v>-3.3912</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.59</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4312</v>
+        <v>-0.4314</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.7616</v>
+        <v>-7.7652</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.51</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.501</v>
+        <v>-0.5012</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.018000000000001</v>
+        <v>-9.021599999999999</v>
       </c>
     </row>
     <row r="262">
@@ -15869,10 +15869,10 @@
         <v>1.61</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2529</v>
+        <v>1.2534</v>
       </c>
       <c r="J292" t="n">
-        <v>25.058</v>
+        <v>25.068</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.44</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0171</v>
+        <v>1.0176</v>
       </c>
       <c r="J293" t="n">
-        <v>20.342</v>
+        <v>20.352</v>
       </c>
     </row>
     <row r="294">
@@ -15946,13 +15946,13 @@
         <v>20</v>
       </c>
       <c r="H294" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I294" t="n">
-        <v>0.7327</v>
+        <v>0.7126</v>
       </c>
       <c r="J294" t="n">
-        <v>14.654</v>
+        <v>14.252</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>1.04</v>
       </c>
       <c r="I295" t="n">
-        <v>0.1378</v>
+        <v>0.1381</v>
       </c>
       <c r="J295" t="n">
-        <v>2.756</v>
+        <v>2.762</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.62</v>
       </c>
       <c r="I296" t="n">
-        <v>-1.0099</v>
+        <v>-1.0096</v>
       </c>
       <c r="J296" t="n">
-        <v>-20.198</v>
+        <v>-20.192</v>
       </c>
     </row>
     <row r="297">
@@ -16066,13 +16066,13 @@
         <v>20</v>
       </c>
       <c r="H297" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0041</v>
+        <v>0.0374</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.082</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>0.98</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.0224</v>
+        <v>-0.0228</v>
       </c>
       <c r="J298" t="n">
-        <v>-0.448</v>
+        <v>-0.456</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.82</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.216</v>
+        <v>-0.2161</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.32</v>
+        <v>-4.322</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.77</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2633</v>
+        <v>-0.2635</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.266</v>
+        <v>-5.27</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.49</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5152</v>
+        <v>-0.5154</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.304</v>
+        <v>-10.308</v>
       </c>
     </row>
     <row r="302">
@@ -17866,13 +17866,13 @@
         <v>15</v>
       </c>
       <c r="H342" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="I342" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0688</v>
       </c>
       <c r="J342" t="n">
-        <v>-1.398</v>
+        <v>-1.032</v>
       </c>
     </row>
     <row r="343">
@@ -17906,13 +17906,13 @@
         <v>15</v>
       </c>
       <c r="H343" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.1755</v>
+        <v>-0.1657</v>
       </c>
       <c r="J343" t="n">
-        <v>-2.6325</v>
+        <v>-2.4855</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.71</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.3066</v>
+        <v>-0.3073</v>
       </c>
       <c r="J344" t="n">
-        <v>-4.599</v>
+        <v>-4.6095</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.61</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3941</v>
+        <v>-0.3949</v>
       </c>
       <c r="J345" t="n">
-        <v>-5.9115</v>
+        <v>-5.9235</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.32</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6483</v>
       </c>
       <c r="J346" t="n">
-        <v>-9.7155</v>
+        <v>-9.724500000000001</v>
       </c>
     </row>
     <row r="347">
@@ -18109,10 +18109,10 @@
         <v>1.71</v>
       </c>
       <c r="I348" t="n">
-        <v>1.3115</v>
+        <v>1.3117</v>
       </c>
       <c r="J348" t="n">
-        <v>19.6725</v>
+        <v>19.6755</v>
       </c>
     </row>
     <row r="349">
@@ -18146,13 +18146,13 @@
         <v>15</v>
       </c>
       <c r="H349" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I349" t="n">
-        <v>0.8925</v>
+        <v>0.8741</v>
       </c>
       <c r="J349" t="n">
-        <v>13.3875</v>
+        <v>13.1115</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>1.39</v>
       </c>
       <c r="I350" t="n">
-        <v>0.8739</v>
+        <v>0.8741</v>
       </c>
       <c r="J350" t="n">
-        <v>13.1085</v>
+        <v>13.1115</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>1.11</v>
       </c>
       <c r="I351" t="n">
-        <v>0.2755</v>
+        <v>0.2758</v>
       </c>
       <c r="J351" t="n">
-        <v>4.1325</v>
+        <v>4.137</v>
       </c>
     </row>
     <row r="352">
@@ -19466,13 +19466,13 @@
         <v>21</v>
       </c>
       <c r="H382" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I382" t="n">
-        <v>0.9851</v>
+        <v>1.0014</v>
       </c>
       <c r="J382" t="n">
-        <v>20.6871</v>
+        <v>21.0294</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.23</v>
       </c>
       <c r="I383" t="n">
-        <v>0.6091</v>
+        <v>0.6088</v>
       </c>
       <c r="J383" t="n">
-        <v>12.7911</v>
+        <v>12.7848</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.22</v>
       </c>
       <c r="I384" t="n">
-        <v>0.588</v>
+        <v>0.5877</v>
       </c>
       <c r="J384" t="n">
-        <v>12.348</v>
+        <v>12.3417</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>1.2</v>
       </c>
       <c r="I385" t="n">
-        <v>0.5455</v>
+        <v>0.5453</v>
       </c>
       <c r="J385" t="n">
-        <v>11.4555</v>
+        <v>11.4513</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.91</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.3525</v>
+        <v>-0.3528</v>
       </c>
       <c r="J386" t="n">
-        <v>-7.4025</v>
+        <v>-7.4088</v>
       </c>
     </row>
     <row r="387">
@@ -19666,13 +19666,13 @@
         <v>21</v>
       </c>
       <c r="H387" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I387" t="n">
-        <v>0.8754</v>
+        <v>0.8608</v>
       </c>
       <c r="J387" t="n">
-        <v>18.3834</v>
+        <v>18.0768</v>
       </c>
     </row>
     <row r="388">
@@ -19786,13 +19786,13 @@
         <v>21</v>
       </c>
       <c r="H390" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2803</v>
+        <v>-0.2706</v>
       </c>
       <c r="J390" t="n">
-        <v>-5.8863</v>
+        <v>-5.6826</v>
       </c>
     </row>
     <row r="391">
@@ -20066,13 +20066,13 @@
         <v>19</v>
       </c>
       <c r="H397" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I397" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.7125</v>
       </c>
       <c r="J397" t="n">
-        <v>13.7047</v>
+        <v>13.5375</v>
       </c>
     </row>
     <row r="398">
@@ -20106,13 +20106,13 @@
         <v>19</v>
       </c>
       <c r="H398" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I398" t="n">
-        <v>0.5321</v>
+        <v>0.5224</v>
       </c>
       <c r="J398" t="n">
-        <v>10.1099</v>
+        <v>9.925599999999999</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>1.25</v>
       </c>
       <c r="I399" t="n">
-        <v>0.3518</v>
+        <v>0.3521</v>
       </c>
       <c r="J399" t="n">
-        <v>6.6842</v>
+        <v>6.6899</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>1.09</v>
       </c>
       <c r="I400" t="n">
-        <v>0.1481</v>
+        <v>0.1487</v>
       </c>
       <c r="J400" t="n">
-        <v>2.8139</v>
+        <v>2.8253</v>
       </c>
     </row>
     <row r="401">
@@ -20226,13 +20226,13 @@
         <v>19</v>
       </c>
       <c r="H401" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I401" t="n">
-        <v>0.0852</v>
+        <v>0.0683</v>
       </c>
       <c r="J401" t="n">
-        <v>1.6188</v>
+        <v>1.2977</v>
       </c>
     </row>
     <row r="402">
@@ -20309,10 +20309,10 @@
         <v>1.84</v>
       </c>
       <c r="I403" t="n">
-        <v>1.4782</v>
+        <v>1.4785</v>
       </c>
       <c r="J403" t="n">
-        <v>23.6512</v>
+        <v>23.656</v>
       </c>
     </row>
     <row r="404">
@@ -20346,13 +20346,13 @@
         <v>16</v>
       </c>
       <c r="H404" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I404" t="n">
-        <v>1.0056</v>
+        <v>0.9903</v>
       </c>
       <c r="J404" t="n">
-        <v>16.0896</v>
+        <v>15.8448</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>1.19</v>
       </c>
       <c r="I405" t="n">
-        <v>0.4787</v>
+        <v>0.479</v>
       </c>
       <c r="J405" t="n">
-        <v>7.6592</v>
+        <v>7.664</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.83</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.6001</v>
+        <v>-0.5998</v>
       </c>
       <c r="J406" t="n">
-        <v>-9.601599999999999</v>
+        <v>-9.5968</v>
       </c>
     </row>
     <row r="407">
@@ -22186,13 +22186,13 @@
         <v>19</v>
       </c>
       <c r="H450" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I450" t="n">
-        <v>0.5646</v>
+        <v>0.5861</v>
       </c>
       <c r="J450" t="n">
-        <v>10.7274</v>
+        <v>11.1359</v>
       </c>
     </row>
     <row r="451">
@@ -22226,13 +22226,13 @@
         <v>19</v>
       </c>
       <c r="H451" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="I451" t="n">
-        <v>0.1706</v>
+        <v>0.1404</v>
       </c>
       <c r="J451" t="n">
-        <v>3.2414</v>
+        <v>2.6676</v>
       </c>
     </row>
     <row r="452">
@@ -25866,13 +25866,13 @@
         <v>22</v>
       </c>
       <c r="H542" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="I542" t="n">
-        <v>1.0314</v>
+        <v>1.016</v>
       </c>
       <c r="J542" t="n">
-        <v>22.6908</v>
+        <v>22.352</v>
       </c>
     </row>
     <row r="543">
@@ -25909,10 +25909,10 @@
         <v>1.28</v>
       </c>
       <c r="I543" t="n">
-        <v>0.7245</v>
+        <v>0.725</v>
       </c>
       <c r="J543" t="n">
-        <v>15.939</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="544">
@@ -25949,10 +25949,10 @@
         <v>1.18</v>
       </c>
       <c r="I544" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5089</v>
       </c>
       <c r="J544" t="n">
-        <v>11.1892</v>
+        <v>11.1958</v>
       </c>
     </row>
     <row r="545">
@@ -25989,10 +25989,10 @@
         <v>0.91</v>
       </c>
       <c r="I545" t="n">
-        <v>-0.3423</v>
+        <v>-0.3419</v>
       </c>
       <c r="J545" t="n">
-        <v>-7.5306</v>
+        <v>-7.5218</v>
       </c>
     </row>
     <row r="546">
@@ -26029,10 +26029,10 @@
         <v>0.89</v>
       </c>
       <c r="I546" t="n">
-        <v>-0.3957</v>
+        <v>-0.3953</v>
       </c>
       <c r="J546" t="n">
-        <v>-8.705399999999999</v>
+        <v>-8.6966</v>
       </c>
     </row>
     <row r="547">
@@ -26269,10 +26269,10 @@
         <v>1.58</v>
       </c>
       <c r="I552" t="n">
-        <v>1.2173</v>
+        <v>1.2178</v>
       </c>
       <c r="J552" t="n">
-        <v>26.7806</v>
+        <v>26.7916</v>
       </c>
     </row>
     <row r="553">
@@ -26306,13 +26306,13 @@
         <v>22</v>
       </c>
       <c r="H553" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="I553" t="n">
-        <v>0.8569</v>
+        <v>0.8375</v>
       </c>
       <c r="J553" t="n">
-        <v>18.8518</v>
+        <v>18.425</v>
       </c>
     </row>
     <row r="554">
@@ -26349,10 +26349,10 @@
         <v>1.24</v>
       </c>
       <c r="I554" t="n">
-        <v>0.6323</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J554" t="n">
-        <v>13.9106</v>
+        <v>13.9172</v>
       </c>
     </row>
     <row r="555">
@@ -26389,10 +26389,10 @@
         <v>0.92</v>
       </c>
       <c r="I555" t="n">
-        <v>-0.3223</v>
+        <v>-0.322</v>
       </c>
       <c r="J555" t="n">
-        <v>-7.0906</v>
+        <v>-7.084</v>
       </c>
     </row>
     <row r="556">
@@ -26429,10 +26429,10 @@
         <v>0.82</v>
       </c>
       <c r="I556" t="n">
-        <v>-0.5759</v>
+        <v>-0.5755</v>
       </c>
       <c r="J556" t="n">
-        <v>-12.6698</v>
+        <v>-12.661</v>
       </c>
     </row>
     <row r="557">
@@ -28069,10 +28069,10 @@
         <v>1.25</v>
       </c>
       <c r="I597" t="n">
-        <v>0.5293</v>
+        <v>0.5299</v>
       </c>
       <c r="J597" t="n">
-        <v>11.6446</v>
+        <v>11.6578</v>
       </c>
     </row>
     <row r="598">
@@ -28109,10 +28109,10 @@
         <v>1.19</v>
       </c>
       <c r="I598" t="n">
-        <v>0.4275</v>
+        <v>0.4281</v>
       </c>
       <c r="J598" t="n">
-        <v>9.404999999999999</v>
+        <v>9.418200000000001</v>
       </c>
     </row>
     <row r="599">
@@ -28149,10 +28149,10 @@
         <v>0.9</v>
       </c>
       <c r="I599" t="n">
-        <v>-0.1432</v>
+        <v>-0.1431</v>
       </c>
       <c r="J599" t="n">
-        <v>-3.1504</v>
+        <v>-3.1482</v>
       </c>
     </row>
     <row r="600">
@@ -28189,10 +28189,10 @@
         <v>0.74</v>
       </c>
       <c r="I600" t="n">
-        <v>-0.3063</v>
+        <v>-0.3062</v>
       </c>
       <c r="J600" t="n">
-        <v>-6.7386</v>
+        <v>-6.7364</v>
       </c>
     </row>
     <row r="601">
@@ -28226,13 +28226,13 @@
         <v>22</v>
       </c>
       <c r="H601" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I601" t="n">
-        <v>-0.3437</v>
+        <v>-0.3527</v>
       </c>
       <c r="J601" t="n">
-        <v>-7.5614</v>
+        <v>-7.7594</v>
       </c>
     </row>
     <row r="602">
@@ -28669,10 +28669,10 @@
         <v>1.69</v>
       </c>
       <c r="I612" t="n">
-        <v>1.3545</v>
+        <v>1.355</v>
       </c>
       <c r="J612" t="n">
-        <v>28.4445</v>
+        <v>28.455</v>
       </c>
     </row>
     <row r="613">
@@ -28709,10 +28709,10 @@
         <v>1.26</v>
       </c>
       <c r="I613" t="n">
-        <v>0.669</v>
+        <v>0.6693</v>
       </c>
       <c r="J613" t="n">
-        <v>14.049</v>
+        <v>14.0553</v>
       </c>
     </row>
     <row r="614">
@@ -28749,10 +28749,10 @@
         <v>1.1</v>
       </c>
       <c r="I614" t="n">
-        <v>0.308</v>
+        <v>0.3083</v>
       </c>
       <c r="J614" t="n">
-        <v>6.468</v>
+        <v>6.4743</v>
       </c>
     </row>
     <row r="615">
@@ -28789,10 +28789,10 @@
         <v>1.03</v>
       </c>
       <c r="I615" t="n">
-        <v>0.1017</v>
+        <v>0.1021</v>
       </c>
       <c r="J615" t="n">
-        <v>2.1357</v>
+        <v>2.1441</v>
       </c>
     </row>
     <row r="616">
@@ -28826,13 +28826,13 @@
         <v>21</v>
       </c>
       <c r="H616" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I616" t="n">
-        <v>-0.0959</v>
+        <v>-0.137</v>
       </c>
       <c r="J616" t="n">
-        <v>-2.0139</v>
+        <v>-2.877</v>
       </c>
     </row>
     <row r="617">
@@ -28869,10 +28869,10 @@
         <v>1.15</v>
       </c>
       <c r="I617" t="n">
-        <v>0.3646</v>
+        <v>0.364</v>
       </c>
       <c r="J617" t="n">
-        <v>7.6566</v>
+        <v>7.644</v>
       </c>
     </row>
     <row r="618">
@@ -28909,10 +28909,10 @@
         <v>0.97</v>
       </c>
       <c r="I618" t="n">
-        <v>-0.0533</v>
+        <v>-0.0535</v>
       </c>
       <c r="J618" t="n">
-        <v>-1.1193</v>
+        <v>-1.1235</v>
       </c>
     </row>
     <row r="619">
@@ -28949,10 +28949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I619" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J619" t="n">
-        <v>-1.9782</v>
+        <v>-1.9803</v>
       </c>
     </row>
     <row r="620">
@@ -28989,10 +28989,10 @@
         <v>0.83</v>
       </c>
       <c r="I620" t="n">
-        <v>-0.2152</v>
+        <v>-0.2154</v>
       </c>
       <c r="J620" t="n">
-        <v>-4.5192</v>
+        <v>-4.5234</v>
       </c>
     </row>
     <row r="621">
@@ -29026,13 +29026,13 @@
         <v>21</v>
       </c>
       <c r="H621" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="I621" t="n">
-        <v>-0.3127</v>
+        <v>-0.3034</v>
       </c>
       <c r="J621" t="n">
-        <v>-6.5667</v>
+        <v>-6.3714</v>
       </c>
     </row>
     <row r="622">
@@ -29666,13 +29666,13 @@
         <v>20</v>
       </c>
       <c r="H637" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I637" t="n">
-        <v>1.5907</v>
+        <v>1.6145</v>
       </c>
       <c r="J637" t="n">
-        <v>31.814</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="638">
@@ -29709,10 +29709,10 @@
         <v>1.2</v>
       </c>
       <c r="I638" t="n">
-        <v>0.5457</v>
+        <v>0.5453</v>
       </c>
       <c r="J638" t="n">
-        <v>10.914</v>
+        <v>10.906</v>
       </c>
     </row>
     <row r="639">
@@ -29749,10 +29749,10 @@
         <v>1.08</v>
       </c>
       <c r="I639" t="n">
-        <v>0.2577</v>
+        <v>0.257</v>
       </c>
       <c r="J639" t="n">
-        <v>5.154</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="640">
@@ -29789,10 +29789,10 @@
         <v>1.05</v>
       </c>
       <c r="I640" t="n">
-        <v>0.1705</v>
+        <v>0.1698</v>
       </c>
       <c r="J640" t="n">
-        <v>3.41</v>
+        <v>3.396</v>
       </c>
     </row>
     <row r="641">
@@ -29829,10 +29829,10 @@
         <v>0.77</v>
       </c>
       <c r="I641" t="n">
-        <v>-0.6922</v>
+        <v>-0.6929</v>
       </c>
       <c r="J641" t="n">
-        <v>-13.844</v>
+        <v>-13.858</v>
       </c>
     </row>
     <row r="642">
@@ -30269,10 +30269,10 @@
         <v>1.53</v>
       </c>
       <c r="I652" t="n">
-        <v>1.1694</v>
+        <v>1.1699</v>
       </c>
       <c r="J652" t="n">
-        <v>33.9126</v>
+        <v>33.9271</v>
       </c>
     </row>
     <row r="653">
@@ -30306,13 +30306,13 @@
         <v>29</v>
       </c>
       <c r="H653" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I653" t="n">
-        <v>0.8569</v>
+        <v>0.8371</v>
       </c>
       <c r="J653" t="n">
-        <v>24.8501</v>
+        <v>24.2759</v>
       </c>
     </row>
     <row r="654">
@@ -30349,10 +30349,10 @@
         <v>1.26</v>
       </c>
       <c r="I654" t="n">
-        <v>0.6905</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J654" t="n">
-        <v>20.0245</v>
+        <v>20.039</v>
       </c>
     </row>
     <row r="655">
@@ -30389,10 +30389,10 @@
         <v>0.8</v>
       </c>
       <c r="I655" t="n">
-        <v>-0.6087</v>
+        <v>-0.6083</v>
       </c>
       <c r="J655" t="n">
-        <v>-17.6523</v>
+        <v>-17.6407</v>
       </c>
     </row>
     <row r="656">
@@ -30429,10 +30429,10 @@
         <v>0.6</v>
       </c>
       <c r="I656" t="n">
-        <v>-1.036</v>
+        <v>-1.0356</v>
       </c>
       <c r="J656" t="n">
-        <v>-30.044</v>
+        <v>-30.0324</v>
       </c>
     </row>
     <row r="657">
@@ -31469,10 +31469,10 @@
         <v>1.13</v>
       </c>
       <c r="I682" t="n">
-        <v>0.335</v>
+        <v>0.3344</v>
       </c>
       <c r="J682" t="n">
-        <v>6.365</v>
+        <v>6.3536</v>
       </c>
     </row>
     <row r="683">
@@ -31506,13 +31506,13 @@
         <v>19</v>
       </c>
       <c r="H683" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I683" t="n">
-        <v>0.0157</v>
+        <v>0.0598</v>
       </c>
       <c r="J683" t="n">
-        <v>0.2983</v>
+        <v>1.1362</v>
       </c>
     </row>
     <row r="684">
@@ -31549,10 +31549,10 @@
         <v>0.86</v>
       </c>
       <c r="I684" t="n">
-        <v>-0.1817</v>
+        <v>-0.1819</v>
       </c>
       <c r="J684" t="n">
-        <v>-3.4523</v>
+        <v>-3.4561</v>
       </c>
     </row>
     <row r="685">
@@ -31589,10 +31589,10 @@
         <v>0.76</v>
       </c>
       <c r="I685" t="n">
-        <v>-0.2814</v>
+        <v>-0.2816</v>
       </c>
       <c r="J685" t="n">
-        <v>-5.3466</v>
+        <v>-5.3504</v>
       </c>
     </row>
     <row r="686">
@@ -31629,10 +31629,10 @@
         <v>0.73</v>
       </c>
       <c r="I686" t="n">
-        <v>-0.3099</v>
+        <v>-0.3101</v>
       </c>
       <c r="J686" t="n">
-        <v>-5.8881</v>
+        <v>-5.8919</v>
       </c>
     </row>
     <row r="687">
@@ -31746,13 +31746,13 @@
         <v>19</v>
       </c>
       <c r="H689" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I689" t="n">
-        <v>1.0034</v>
+        <v>1.0187</v>
       </c>
       <c r="J689" t="n">
-        <v>19.0646</v>
+        <v>19.3553</v>
       </c>
     </row>
     <row r="690">
@@ -31826,13 +31826,13 @@
         <v>19</v>
       </c>
       <c r="H691" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="I691" t="n">
-        <v>-0.5335</v>
+        <v>-0.5576</v>
       </c>
       <c r="J691" t="n">
-        <v>-10.1365</v>
+        <v>-10.5944</v>
       </c>
     </row>
     <row r="692">
@@ -32666,13 +32666,13 @@
         <v>18</v>
       </c>
       <c r="H712" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I712" t="n">
-        <v>1.7137</v>
+        <v>1.7028</v>
       </c>
       <c r="J712" t="n">
-        <v>30.8466</v>
+        <v>30.6504</v>
       </c>
     </row>
     <row r="713">
@@ -32706,13 +32706,13 @@
         <v>18</v>
       </c>
       <c r="H713" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I713" t="n">
-        <v>0.738</v>
+        <v>0.7189</v>
       </c>
       <c r="J713" t="n">
-        <v>13.284</v>
+        <v>12.9402</v>
       </c>
     </row>
     <row r="714">
@@ -32749,10 +32749,10 @@
         <v>1.26</v>
       </c>
       <c r="I714" t="n">
-        <v>0.6582</v>
+        <v>0.6587</v>
       </c>
       <c r="J714" t="n">
-        <v>11.8476</v>
+        <v>11.8566</v>
       </c>
     </row>
     <row r="715">
@@ -32789,10 +32789,10 @@
         <v>1.13</v>
       </c>
       <c r="I715" t="n">
-        <v>0.3681</v>
+        <v>0.3687</v>
       </c>
       <c r="J715" t="n">
-        <v>6.6258</v>
+        <v>6.6366</v>
       </c>
     </row>
     <row r="716">
@@ -32829,10 +32829,10 @@
         <v>0.87</v>
       </c>
       <c r="I716" t="n">
-        <v>-0.476</v>
+        <v>-0.4754</v>
       </c>
       <c r="J716" t="n">
-        <v>-8.568</v>
+        <v>-8.5572</v>
       </c>
     </row>
     <row r="717">
